--- a/employment/06_staggered_did_analysis.xlsx
+++ b/employment/06_staggered_did_analysis.xlsx
@@ -23,7 +23,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -43,6 +43,9 @@
     <font>
       <b val="1"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <sz val="10"/>
     </font>
     <font>
       <b val="1"/>
@@ -113,7 +116,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -128,6 +131,7 @@
     <xf numFmtId="165" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -135,7 +139,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -502,25 +506,29 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="10" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="8" customWidth="1" min="9" max="9"/>
     <col width="8" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="11" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="8" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Staggered DiD (Callaway &amp; Sant'Anna 2021) — Overall ATT</t>
+          <t>Staggered DiD (Callaway &amp; Sant'Anna 2021) — overall ATT, dynamic and simple aggregations reported separately</t>
         </is>
       </c>
     </row>
@@ -542,7 +550,8 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ATT</t>
+          <t>ATT
+(dynamic agg)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -573,6 +582,29 @@
       <c r="J2" s="2" t="inlineStr">
         <is>
           <t>Control</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>ATT
+(simple agg)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>SE
+(simple)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>p-value
+(simple)</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>N obs</t>
         </is>
       </c>
     </row>
@@ -593,25 +625,37 @@
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>1509.301780416631</v>
+        <v>1525.913597708414</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>1365.725483722516</v>
+        <v>1422.802424460011</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>-1167.5201676795</v>
+        <v>-1262.779154233207</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>4186.123728512762</v>
+        <v>4314.606349650035</v>
       </c>
       <c r="H3" s="5" t="n">
-        <v>0.2691040317613465</v>
+        <v>0.2835087666036538</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>18</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="K3" s="4" t="n">
+        <v>1996.732867885565</v>
+      </c>
+      <c r="L3" s="4" t="n">
+        <v>1204.077624548094</v>
+      </c>
+      <c r="M3" s="5" t="n">
+        <v>0.09725509554659006</v>
+      </c>
+      <c r="N3" s="3" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="4">
@@ -631,25 +675,37 @@
         </is>
       </c>
       <c r="D4" s="4" t="n">
-        <v>1295.154729058684</v>
+        <v>1306.052974824788</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>1103.582893210394</v>
+        <v>1058.637711472778</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>-867.8677416336886</v>
+        <v>-768.8769396618577</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>3458.177199751056</v>
+        <v>3380.982889311433</v>
       </c>
       <c r="H4" s="5" t="n">
-        <v>0.2405589685062428</v>
+        <v>0.2173106187349294</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>18</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="K4" s="4" t="n">
+        <v>1592.525162180984</v>
+      </c>
+      <c r="L4" s="4" t="n">
+        <v>902.941950141444</v>
+      </c>
+      <c r="M4" s="5" t="n">
+        <v>0.07778129882883977</v>
+      </c>
+      <c r="N4" s="3" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="5">
@@ -669,25 +725,37 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>7326.83919331994</v>
+        <v>7409.103796310913</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>5845.29764400248</v>
+        <v>5846.014917717816</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>-4129.944188924921</v>
+        <v>-4049.085442416007</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>18783.6225755648</v>
+        <v>18867.29303503783</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>0.2100388198706151</v>
+        <v>0.2050205840917045</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>18</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>9106.220456094919</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>5098.57515885779</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>0.07409401136515736</v>
+      </c>
+      <c r="N5" s="3" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="6">
@@ -707,25 +775,37 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>20321.88701235558</v>
+        <v>21049.17847544492</v>
       </c>
       <c r="E6" s="6" t="n">
-        <v>5891.405705529594</v>
+        <v>5858.150569744168</v>
       </c>
       <c r="F6" s="6" t="n">
-        <v>8774.731829517574</v>
+        <v>9567.203358746352</v>
       </c>
       <c r="G6" s="6" t="n">
-        <v>31869.04219519359</v>
+        <v>32531.15359214349</v>
       </c>
       <c r="H6" s="7" t="n">
-        <v>0.0005618082907883348</v>
+        <v>0.0003267119344336766</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>18</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>11180.45869763629</v>
+      </c>
+      <c r="L6" s="4" t="n">
+        <v>4215.517454477238</v>
+      </c>
+      <c r="M6" s="5" t="n">
+        <v>0.007996560058550095</v>
+      </c>
+      <c r="N6" s="3" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="7">
@@ -745,25 +825,37 @@
         </is>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2041.463971255961</v>
+        <v>2100.412064036522</v>
       </c>
       <c r="E7" s="6" t="n">
-        <v>449.0162302228823</v>
+        <v>433.6539619635554</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>1161.392160019112</v>
+        <v>1250.450298587954</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>2921.53578249281</v>
+        <v>2950.373829485091</v>
       </c>
       <c r="H7" s="7" t="n">
-        <v>5.453863181514862e-06</v>
+        <v>1.275582435678047e-06</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>18</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>969.5966044689123</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>445.6389597749474</v>
+      </c>
+      <c r="M7" s="5" t="n">
+        <v>0.02957435583540091</v>
+      </c>
+      <c r="N7" s="3" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="8">
@@ -783,25 +875,37 @@
         </is>
       </c>
       <c r="D8" s="4" t="n">
-        <v>10439.78252157506</v>
+        <v>10662.22337287319</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>6052.318324559882</v>
+        <v>5964.774282339878</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>-1422.761394562309</v>
+        <v>-1028.734220512972</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>22302.32643771243</v>
+        <v>22353.18096625935</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>0.08454136667455758</v>
+        <v>0.07385158628974908</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>18</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>33</v>
+        <v>31</v>
+      </c>
+      <c r="K8" s="4" t="n">
+        <v>5720.559293608146</v>
+      </c>
+      <c r="L8" s="4" t="n">
+        <v>5390.265184656586</v>
+      </c>
+      <c r="M8" s="5" t="n">
+        <v>0.2885644708879611</v>
+      </c>
+      <c r="N8" s="3" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="9">
@@ -821,25 +925,37 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3824.717824939853</v>
+        <v>3812.983545168483</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1156.035834511485</v>
+        <v>1175.072580737582</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>1558.887589297342</v>
+        <v>1509.841286922822</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>6090.548060582363</v>
+        <v>6116.125803414145</v>
       </c>
       <c r="H9" s="7" t="n">
-        <v>0.0009380493142234769</v>
+        <v>0.001174952014582731</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>13</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>2070.224431107091</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>1146.883003791257</v>
+      </c>
+      <c r="M9" s="5" t="n">
+        <v>0.07106095573604843</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="10">
@@ -859,25 +975,37 @@
         </is>
       </c>
       <c r="D10" s="6" t="n">
-        <v>2936.61698294259</v>
+        <v>2928.262299095118</v>
       </c>
       <c r="E10" s="6" t="n">
-        <v>788.0968031092832</v>
+        <v>812.9693365770252</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>1391.947248848395</v>
+        <v>1334.842399404148</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>4481.286717036785</v>
+        <v>4521.682198786087</v>
       </c>
       <c r="H10" s="7" t="n">
-        <v>0.0001943777439226135</v>
+        <v>0.0003158579604420897</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>13</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="K10" s="4" t="n">
+        <v>1580.108347463439</v>
+      </c>
+      <c r="L10" s="4" t="n">
+        <v>840.9514838482725</v>
+      </c>
+      <c r="M10" s="5" t="n">
+        <v>0.06025090552488743</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="11">
@@ -897,25 +1025,37 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>16049.92207744789</v>
+        <v>16023.98605074813</v>
       </c>
       <c r="E11" s="6" t="n">
-        <v>5319.093939407598</v>
+        <v>5440.546215615183</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>5624.497956208996</v>
+        <v>5360.515468142374</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>26475.34619868678</v>
+        <v>26687.45663335389</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.002549392246122162</v>
+        <v>0.003226521505043101</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>13</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="K11" s="4" t="n">
+        <v>8860.862450418372</v>
+      </c>
+      <c r="L11" s="4" t="n">
+        <v>5007.296663769441</v>
+      </c>
+      <c r="M11" s="5" t="n">
+        <v>0.07679545436662183</v>
+      </c>
+      <c r="N11" s="3" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="12">
@@ -935,25 +1075,37 @@
         </is>
       </c>
       <c r="D12" s="4" t="n">
-        <v>14061.41994373546</v>
+        <v>14118.80527742138</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>11133.14942717456</v>
+        <v>9702.114361159516</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>-7759.552933526671</v>
+        <v>-4897.338870451274</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>35882.3928209976</v>
+        <v>33134.94942529403</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>0.2065810382244413</v>
+        <v>0.1456056724957704</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>13</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="K12" s="4" t="n">
+        <v>8130.233967479151</v>
+      </c>
+      <c r="L12" s="4" t="n">
+        <v>7587.321195123304</v>
+      </c>
+      <c r="M12" s="5" t="n">
+        <v>0.2839198358624646</v>
+      </c>
+      <c r="N12" s="3" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="13">
@@ -973,25 +1125,37 @@
         </is>
       </c>
       <c r="D13" s="6" t="n">
-        <v>1184.613206172186</v>
+        <v>1179.977722501337</v>
       </c>
       <c r="E13" s="6" t="n">
-        <v>535.4189768116714</v>
+        <v>546.8652161104235</v>
       </c>
       <c r="F13" s="6" t="n">
-        <v>135.19201162131</v>
+        <v>108.1218989249069</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>2234.034400723062</v>
+        <v>2251.833546077767</v>
       </c>
       <c r="H13" s="7" t="n">
-        <v>0.02693230120776247</v>
+        <v>0.03095021853262403</v>
       </c>
       <c r="I13" s="3" t="n">
         <v>13</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="K13" s="4" t="n">
+        <v>98.13985771344618</v>
+      </c>
+      <c r="L13" s="4" t="n">
+        <v>554.3409923879377</v>
+      </c>
+      <c r="M13" s="5" t="n">
+        <v>0.8594779219494573</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="14">
@@ -1011,25 +1175,37 @@
         </is>
       </c>
       <c r="D14" s="4" t="n">
-        <v>17864.88832919002</v>
+        <v>17883.07750382266</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>13175.25189783218</v>
+        <v>13542.86205053865</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>-7958.605390561042</v>
+        <v>-8660.932115233092</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>43688.38204894109</v>
+        <v>44427.08712287841</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>0.1751173590838269</v>
+        <v>0.186674833255325</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>13</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>10784.27822051015</v>
+      </c>
+      <c r="L14" s="4" t="n">
+        <v>11371.22780109167</v>
+      </c>
+      <c r="M14" s="5" t="n">
+        <v>0.3429345515984192</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>438</v>
       </c>
     </row>
     <row r="16">
@@ -1054,66 +1230,126 @@
     <row r="18">
       <c r="A18" s="9" t="inlineStr">
         <is>
-          <t>Treatment</t>
+          <t>Universe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>First year NEW DC capacity (since 2016) &gt; threshold</t>
+          <t>the 48 contiguous states plus the District of Columbia (49 units)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="9" t="inlineStr">
         <is>
-          <t>Control</t>
+          <t>Treatment</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Never-treated states (never exceeded threshold by 2024)</t>
+          <t>First year NEW DC capacity (since 2016) &gt; threshold</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="9" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bootstrapped (1000 iterations)</t>
+          <t>Never-treated units (never exceeded threshold by 2024)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="9" t="inlineStr">
         <is>
-          <t>Period</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2016–2024</t>
+          <t>Bootstrapped (1000 iterations), seed 20260728</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="9" t="inlineStr">
         <is>
-          <t>ATT</t>
+          <t>Period</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Average treatment effect on the treated</t>
+          <t>2016–2024; Michigan absent 2022–2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>ATT (dynamic agg)</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>average of the event-study ATT(e) for e &gt;= 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="10" t="inlineStr"/>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>This is the column the published table contained, mislabelled</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr"/>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>as the simple aggregation (csdid aggte() returns self).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>ATT (simple agg)</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>group-size-weighted average of all post ATT(g,t).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>csdid version</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>pinned 0.2.9; point estimates are not stable</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr"/>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>across csdid versions -- 0.4.2 moves 1 GW raw 5182 by 6.5%</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1141,47 +1377,47 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="B1" s="10" t="inlineStr">
+      <c r="B1" s="11" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="C1" s="10" t="inlineStr">
+      <c r="C1" s="11" t="inlineStr">
         <is>
           <t>Y Variable</t>
         </is>
       </c>
-      <c r="D1" s="10" t="inlineStr">
+      <c r="D1" s="11" t="inlineStr">
         <is>
           <t>Event Time</t>
         </is>
       </c>
-      <c r="E1" s="10" t="inlineStr">
+      <c r="E1" s="11" t="inlineStr">
         <is>
           <t>ATT</t>
         </is>
       </c>
-      <c r="F1" s="10" t="inlineStr">
+      <c r="F1" s="11" t="inlineStr">
         <is>
           <t>SE</t>
         </is>
       </c>
-      <c r="G1" s="10" t="inlineStr">
+      <c r="G1" s="11" t="inlineStr">
         <is>
           <t>CI95 Lower</t>
         </is>
       </c>
-      <c r="H1" s="10" t="inlineStr">
+      <c r="H1" s="11" t="inlineStr">
         <is>
           <t>CI95 Upper</t>
         </is>
       </c>
-      <c r="I1" s="10" t="inlineStr">
+      <c r="I1" s="11" t="inlineStr">
         <is>
           <t>Sig</t>
         </is>
@@ -1206,19 +1442,23 @@
       <c r="D2" s="3" t="n">
         <v>-7</v>
       </c>
-      <c r="E2" s="4" t="n">
-        <v>-401.5310283687931</v>
-      </c>
-      <c r="F2" s="4" t="n">
-        <v>210.3093101741842</v>
+      <c r="E2" s="12" t="n">
+        <v>-275.3244680851071</v>
+      </c>
+      <c r="F2" s="12" t="n">
+        <v>131.7079647601184</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>-813.7372763101941</v>
+        <v>-533.4720790149393</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>10.67521957260789</v>
-      </c>
-      <c r="I2" s="3" t="inlineStr"/>
+        <v>-17.17685715527506</v>
+      </c>
+      <c r="I2" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1240,16 +1480,16 @@
         <v>-6</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>-246.2099955673759</v>
+        <v>-188.3425647548572</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>153.9450423461032</v>
+        <v>160.0586729288577</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-547.9422785657381</v>
+        <v>-502.0575636954184</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>55.52228743098624</v>
+        <v>125.3724341857039</v>
       </c>
       <c r="I3" s="3" t="inlineStr"/>
     </row>
@@ -1273,16 +1513,16 @@
         <v>-5</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>206.4127856420622</v>
+        <v>281.2682221098752</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>419.1213263166192</v>
+        <v>455.0055660472069</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-615.0650139385115</v>
+        <v>-610.5426873426502</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>1027.890585222636</v>
+        <v>1173.079131562401</v>
       </c>
       <c r="I4" s="3" t="inlineStr"/>
     </row>
@@ -1306,16 +1546,16 @@
         <v>-4</v>
       </c>
       <c r="E5" s="4" t="n">
-        <v>277.5287817124735</v>
+        <v>333.1118987843546</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>478.5355271257372</v>
+        <v>493.033264448468</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-660.4008514539714</v>
+        <v>-633.2332995346427</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>1215.458414878918</v>
+        <v>1299.457097103352</v>
       </c>
       <c r="I5" s="3" t="inlineStr"/>
     </row>
@@ -1339,16 +1579,16 @@
         <v>-3</v>
       </c>
       <c r="E6" s="4" t="n">
-        <v>392.9482087989773</v>
+        <v>418.4922211426799</v>
       </c>
       <c r="F6" s="4" t="n">
-        <v>406.255862826702</v>
+        <v>404.6969271921035</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>-403.3132823413585</v>
+        <v>-374.7137561538431</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1189.209699939313</v>
+        <v>1211.698198439203</v>
       </c>
       <c r="I6" s="3" t="inlineStr"/>
     </row>
@@ -1372,16 +1612,16 @@
         <v>-2</v>
       </c>
       <c r="E7" s="4" t="n">
-        <v>329.7393186617354</v>
+        <v>346.6602201587825</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>193.3604248989635</v>
+        <v>211.9932834478038</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>-49.24711414023312</v>
+        <v>-68.84661539891289</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>708.7257514637038</v>
+        <v>762.167055716478</v>
       </c>
       <c r="I7" s="3" t="inlineStr"/>
     </row>
@@ -1405,16 +1645,16 @@
         <v>-1</v>
       </c>
       <c r="E8" s="4" t="n">
-        <v>345.4205726751746</v>
+        <v>347.9115088834265</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>185.4033027209757</v>
+        <v>185.5082214999395</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>-17.96990065793767</v>
+        <v>-15.6846052564548</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>708.8110460082869</v>
+        <v>711.5076230233078</v>
       </c>
       <c r="I8" s="3" t="inlineStr"/>
     </row>
@@ -1438,16 +1678,16 @@
         <v>0</v>
       </c>
       <c r="E9" s="4" t="n">
-        <v>535.5948599163208</v>
+        <v>539.1899649601559</v>
       </c>
       <c r="F9" s="4" t="n">
-        <v>637.0272593278626</v>
+        <v>655.4953928725197</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>-712.9785683662898</v>
+        <v>-745.5810050699828</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>1784.168288198931</v>
+        <v>1823.960934990294</v>
       </c>
       <c r="I9" s="3" t="inlineStr"/>
     </row>
@@ -1471,16 +1711,16 @@
         <v>1</v>
       </c>
       <c r="E10" s="4" t="n">
-        <v>1699.255880959631</v>
+        <v>1700.413991260881</v>
       </c>
       <c r="F10" s="4" t="n">
-        <v>1126.745950692159</v>
+        <v>1131.951403219279</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>-509.1661823970014</v>
+        <v>-518.2107590489052</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>3907.677944316262</v>
+        <v>3919.038741570667</v>
       </c>
       <c r="I10" s="3" t="inlineStr"/>
     </row>
@@ -1504,16 +1744,16 @@
         <v>2</v>
       </c>
       <c r="E11" s="4" t="n">
-        <v>2399.880634502293</v>
+        <v>2398.939508778562</v>
       </c>
       <c r="F11" s="4" t="n">
-        <v>2098.471220663327</v>
+        <v>1928.07250296428</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>-1713.122957997829</v>
+        <v>-1380.082597031427</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>6512.884227002414</v>
+        <v>6177.961614588552</v>
       </c>
       <c r="I11" s="3" t="inlineStr"/>
     </row>
@@ -1537,16 +1777,16 @@
         <v>3</v>
       </c>
       <c r="E12" s="4" t="n">
-        <v>2846.097332779529</v>
+        <v>2844.510906805488</v>
       </c>
       <c r="F12" s="4" t="n">
-        <v>2090.579830990341</v>
+        <v>2083.275505139292</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>-1251.439135961538</v>
+        <v>-1238.709083267525</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>6943.633801520597</v>
+        <v>6927.730896878501</v>
       </c>
       <c r="I12" s="3" t="inlineStr"/>
     </row>
@@ -1570,16 +1810,16 @@
         <v>4</v>
       </c>
       <c r="E13" s="4" t="n">
-        <v>2997.32158498193</v>
+        <v>2994.588135577041</v>
       </c>
       <c r="F13" s="4" t="n">
-        <v>2076.204708515819</v>
+        <v>1949.518139622021</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>-1072.039643709075</v>
+        <v>-826.4674180821198</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>7066.682813672935</v>
+        <v>6815.643689236202</v>
       </c>
       <c r="I13" s="3" t="inlineStr"/>
     </row>
@@ -1603,16 +1843,16 @@
         <v>5</v>
       </c>
       <c r="E14" s="4" t="n">
-        <v>4735.246767275457</v>
+        <v>4737.21875244379</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>2883.101573294387</v>
+        <v>2894.499525938905</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>-915.6323163815414</v>
+        <v>-936.0003183964627</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>10386.12585093246</v>
+        <v>10410.43782328404</v>
       </c>
       <c r="I14" s="3" t="inlineStr"/>
     </row>
@@ -1636,16 +1876,16 @@
         <v>6</v>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1097.268919028999</v>
+        <v>1129.2519125224</v>
       </c>
       <c r="F15" s="4" t="n">
-        <v>6439.708529316564</v>
+        <v>6902.505594907355</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>-11524.55979843147</v>
+        <v>-12399.65905349601</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>13719.09763648946</v>
+        <v>14658.16287854082</v>
       </c>
       <c r="I15" s="3" t="inlineStr"/>
     </row>
@@ -1668,19 +1908,19 @@
       <c r="D16" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="E16" s="11" t="n">
-        <v>-4236.251736111112</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>691.3583118446505</v>
+      <c r="E16" s="12" t="n">
+        <v>-4136.804390681005</v>
+      </c>
+      <c r="F16" s="12" t="n">
+        <v>677.8422060708889</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>-5591.314027326627</v>
+        <v>-5465.375114579947</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-2881.189444895597</v>
-      </c>
-      <c r="I16" s="12" t="inlineStr">
+        <v>-2808.233666782063</v>
+      </c>
+      <c r="I16" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1705,19 +1945,19 @@
       <c r="D17" s="3" t="n">
         <v>-7</v>
       </c>
-      <c r="E17" s="11" t="n">
-        <v>-306.3645610297684</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>146.7545057615746</v>
+      <c r="E17" s="12" t="n">
+        <v>-216.8931769233062</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <v>98.93058117236068</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>-594.0033923224545</v>
+        <v>-410.7971160211331</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-18.72572973708225</v>
-      </c>
-      <c r="I17" s="12" t="inlineStr">
+        <v>-22.98923782547931</v>
+      </c>
+      <c r="I17" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -1743,16 +1983,16 @@
         <v>-6</v>
       </c>
       <c r="E18" s="4" t="n">
-        <v>-198.5088552792922</v>
+        <v>-157.1979616228538</v>
       </c>
       <c r="F18" s="4" t="n">
-        <v>117.6577631795448</v>
+        <v>114.2444348820413</v>
       </c>
       <c r="G18" s="4" t="n">
-        <v>-429.1180711112</v>
+        <v>-381.1170539916548</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>32.10036055261574</v>
+        <v>66.72113074594714</v>
       </c>
       <c r="I18" s="3" t="inlineStr"/>
     </row>
@@ -1776,16 +2016,16 @@
         <v>-5</v>
       </c>
       <c r="E19" s="4" t="n">
-        <v>168.0627432425046</v>
+        <v>221.03265616011</v>
       </c>
       <c r="F19" s="4" t="n">
-        <v>340.5912098797922</v>
+        <v>353.0032333429686</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>-499.496028121888</v>
+        <v>-470.8536811921084</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>835.6215146068973</v>
+        <v>912.9189935123285</v>
       </c>
       <c r="I19" s="3" t="inlineStr"/>
     </row>
@@ -1809,16 +2049,16 @@
         <v>-4</v>
       </c>
       <c r="E20" s="4" t="n">
-        <v>209.1753319635837</v>
+        <v>248.4486700857233</v>
       </c>
       <c r="F20" s="4" t="n">
-        <v>370.8976413783386</v>
+        <v>374.8302262104774</v>
       </c>
       <c r="G20" s="4" t="n">
-        <v>-517.78404513796</v>
+        <v>-486.2185732868124</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>936.1347090651275</v>
+        <v>983.115913458259</v>
       </c>
       <c r="I20" s="3" t="inlineStr"/>
     </row>
@@ -1842,16 +2082,16 @@
         <v>-3</v>
       </c>
       <c r="E21" s="4" t="n">
-        <v>287.6566781481663</v>
+        <v>306.1334533265837</v>
       </c>
       <c r="F21" s="4" t="n">
-        <v>306.2835315068013</v>
+        <v>305.3026198055067</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>-312.6590436051642</v>
+        <v>-292.2596814922093</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>887.9723999014968</v>
+        <v>904.5265881453766</v>
       </c>
       <c r="I21" s="3" t="inlineStr"/>
     </row>
@@ -1875,16 +2115,16 @@
         <v>-2</v>
       </c>
       <c r="E22" s="4" t="n">
-        <v>237.6835484940758</v>
+        <v>249.7386694892955</v>
       </c>
       <c r="F22" s="4" t="n">
-        <v>156.4096760786051</v>
+        <v>161.4354137827914</v>
       </c>
       <c r="G22" s="4" t="n">
-        <v>-68.87941661999031</v>
+        <v>-66.67474152497556</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>544.2465136081419</v>
+        <v>566.1520805035666</v>
       </c>
       <c r="I22" s="3" t="inlineStr"/>
     </row>
@@ -1908,16 +2148,16 @@
         <v>-1</v>
       </c>
       <c r="E23" s="4" t="n">
-        <v>259.4606722845134</v>
+        <v>261.3020065588398</v>
       </c>
       <c r="F23" s="4" t="n">
-        <v>132.8910487906252</v>
+        <v>140.5250667511047</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>-1.005783345112036</v>
+        <v>-14.12712427332548</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>519.9271279141387</v>
+        <v>536.7311373910049</v>
       </c>
       <c r="I23" s="3" t="inlineStr"/>
     </row>
@@ -1941,16 +2181,16 @@
         <v>0</v>
       </c>
       <c r="E24" s="4" t="n">
-        <v>431.3998580431041</v>
+        <v>433.8582693198843</v>
       </c>
       <c r="F24" s="4" t="n">
-        <v>528.8045751349147</v>
+        <v>517.9778885012209</v>
       </c>
       <c r="G24" s="4" t="n">
-        <v>-605.0571092213286</v>
+        <v>-581.3783921425088</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>1467.856825307537</v>
+        <v>1449.094930782277</v>
       </c>
       <c r="I24" s="3" t="inlineStr"/>
     </row>
@@ -1974,16 +2214,16 @@
         <v>1</v>
       </c>
       <c r="E25" s="4" t="n">
-        <v>1337.851158430178</v>
+        <v>1338.312629696692</v>
       </c>
       <c r="F25" s="4" t="n">
-        <v>830.1659591570699</v>
+        <v>857.5625643857502</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>-289.2741215176795</v>
+        <v>-342.5099964993788</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>2964.976438378035</v>
+        <v>3019.135255892762</v>
       </c>
       <c r="I25" s="3" t="inlineStr"/>
     </row>
@@ -2007,16 +2247,16 @@
         <v>2</v>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1893.883270313508</v>
+        <v>1892.620095363764</v>
       </c>
       <c r="F26" s="4" t="n">
-        <v>1600.347743759113</v>
+        <v>1468.392373000794</v>
       </c>
       <c r="G26" s="4" t="n">
-        <v>-1242.798307454353</v>
+        <v>-985.4289557177917</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>5030.564848081369</v>
+        <v>4770.66914644532</v>
       </c>
       <c r="I26" s="3" t="inlineStr"/>
     </row>
@@ -2040,16 +2280,16 @@
         <v>3</v>
       </c>
       <c r="E27" s="4" t="n">
-        <v>2238.2596177321</v>
+        <v>2236.468290606154</v>
       </c>
       <c r="F27" s="4" t="n">
-        <v>1522.230251334443</v>
+        <v>1542.852583082317</v>
       </c>
       <c r="G27" s="4" t="n">
-        <v>-745.3116748834077</v>
+        <v>-787.5227722351865</v>
       </c>
       <c r="H27" s="4" t="n">
-        <v>5221.830910347608</v>
+        <v>5260.459353447495</v>
       </c>
       <c r="I27" s="3" t="inlineStr"/>
     </row>
@@ -2073,16 +2313,16 @@
         <v>4</v>
       </c>
       <c r="E28" s="4" t="n">
-        <v>2371.635712360988</v>
+        <v>2369.094874860609</v>
       </c>
       <c r="F28" s="4" t="n">
-        <v>1559.256817111853</v>
+        <v>1518.795626914873</v>
       </c>
       <c r="G28" s="4" t="n">
-        <v>-684.5076491782434</v>
+        <v>-607.7445538925417</v>
       </c>
       <c r="H28" s="4" t="n">
-        <v>5427.779073900219</v>
+        <v>5345.93430361376</v>
       </c>
       <c r="I28" s="3" t="inlineStr"/>
     </row>
@@ -2106,16 +2346,16 @@
         <v>5</v>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3789.577424195807</v>
+        <v>3790.307014415552</v>
       </c>
       <c r="F29" s="4" t="n">
-        <v>2102.974847326402</v>
+        <v>2105.659014910094</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>-332.2532765639407</v>
+        <v>-336.7846548082334</v>
       </c>
       <c r="H29" s="4" t="n">
-        <v>7911.408124955555</v>
+        <v>7917.398683639337</v>
       </c>
       <c r="I29" s="3" t="inlineStr"/>
     </row>
@@ -2139,16 +2379,16 @@
         <v>6</v>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1171.75929132439</v>
+        <v>1193.183422878514</v>
       </c>
       <c r="F30" s="4" t="n">
-        <v>3301.518742168378</v>
+        <v>5249.739555692654</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>-5299.21744332563</v>
+        <v>-9096.306106279088</v>
       </c>
       <c r="H30" s="4" t="n">
-        <v>7642.73602597441</v>
+        <v>11482.67295203612</v>
       </c>
       <c r="I30" s="3" t="inlineStr"/>
     </row>
@@ -2171,19 +2411,19 @@
       <c r="D31" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="E31" s="11" t="n">
-        <v>-2873.128499930604</v>
-      </c>
-      <c r="F31" s="11" t="n">
-        <v>488.5907516879315</v>
+      <c r="E31" s="12" t="n">
+        <v>-2805.420798542867</v>
+      </c>
+      <c r="F31" s="12" t="n">
+        <v>475.6235935097503</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>-3830.766373238949</v>
+        <v>-3737.643041821978</v>
       </c>
       <c r="H31" s="4" t="n">
-        <v>-1915.490626622258</v>
-      </c>
-      <c r="I31" s="12" t="inlineStr">
+        <v>-1873.198555263757</v>
+      </c>
+      <c r="I31" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2208,19 +2448,19 @@
       <c r="D32" s="3" t="n">
         <v>-7</v>
       </c>
-      <c r="E32" s="11" t="n">
-        <v>-1716.58671816308</v>
-      </c>
-      <c r="F32" s="11" t="n">
-        <v>782.0959667819614</v>
+      <c r="E32" s="12" t="n">
+        <v>-1232.347180593567</v>
+      </c>
+      <c r="F32" s="12" t="n">
+        <v>551.8941688866224</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>-3249.494813055724</v>
+        <v>-2314.059751611347</v>
       </c>
       <c r="H32" s="4" t="n">
-        <v>-183.678623270436</v>
-      </c>
-      <c r="I32" s="12" t="inlineStr">
+        <v>-150.634609575787</v>
+      </c>
+      <c r="I32" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2246,16 +2486,16 @@
         <v>-6</v>
       </c>
       <c r="E33" s="4" t="n">
-        <v>-1133.264174552395</v>
+        <v>-905.1816114751921</v>
       </c>
       <c r="F33" s="4" t="n">
-        <v>641.2363882531951</v>
+        <v>637.8582932174178</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>-2390.087495528658</v>
+        <v>-2155.383866181331</v>
       </c>
       <c r="H33" s="4" t="n">
-        <v>123.5591464238669</v>
+        <v>345.0206432309467</v>
       </c>
       <c r="I33" s="3" t="inlineStr"/>
     </row>
@@ -2279,16 +2519,16 @@
         <v>-5</v>
       </c>
       <c r="E34" s="4" t="n">
-        <v>854.6171937643693</v>
+        <v>1144.397110779847</v>
       </c>
       <c r="F34" s="4" t="n">
-        <v>1831.35292535988</v>
+        <v>1859.174594494802</v>
       </c>
       <c r="G34" s="4" t="n">
-        <v>-2734.834539940995</v>
+        <v>-2499.585094429965</v>
       </c>
       <c r="H34" s="4" t="n">
-        <v>4444.068927469733</v>
+        <v>4788.379315989659</v>
       </c>
       <c r="I34" s="3" t="inlineStr"/>
     </row>
@@ -2312,16 +2552,16 @@
         <v>-4</v>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1185.280996699178</v>
+        <v>1400.71224145996</v>
       </c>
       <c r="F35" s="4" t="n">
-        <v>2007.723266719794</v>
+        <v>2107.650359732088</v>
       </c>
       <c r="G35" s="4" t="n">
-        <v>-2749.856606071619</v>
+        <v>-2730.282463614933</v>
       </c>
       <c r="H35" s="4" t="n">
-        <v>5120.418599469975</v>
+        <v>5531.706946534853</v>
       </c>
       <c r="I35" s="3" t="inlineStr"/>
     </row>
@@ -2345,16 +2585,16 @@
         <v>-3</v>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1610.557924271055</v>
+        <v>1717.327618474376</v>
       </c>
       <c r="F36" s="4" t="n">
-        <v>1773.522285054757</v>
+        <v>1746.74383687467</v>
       </c>
       <c r="G36" s="4" t="n">
-        <v>-1865.545754436269</v>
+        <v>-1706.290301799978</v>
       </c>
       <c r="H36" s="4" t="n">
-        <v>5086.661602978379</v>
+        <v>5140.945538748731</v>
       </c>
       <c r="I36" s="3" t="inlineStr"/>
     </row>
@@ -2378,16 +2618,16 @@
         <v>-2</v>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1341.353549039804</v>
+        <v>1411.750359535632</v>
       </c>
       <c r="F37" s="4" t="n">
-        <v>878.4093191371828</v>
+        <v>917.3590108847712</v>
       </c>
       <c r="G37" s="4" t="n">
-        <v>-380.3287164690739</v>
+        <v>-386.2733017985199</v>
       </c>
       <c r="H37" s="4" t="n">
-        <v>3063.035814548683</v>
+        <v>3209.774020869783</v>
       </c>
       <c r="I37" s="3" t="inlineStr"/>
     </row>
@@ -2410,23 +2650,19 @@
       <c r="D38" s="3" t="n">
         <v>-1</v>
       </c>
-      <c r="E38" s="11" t="n">
-        <v>1501.372337708014</v>
-      </c>
-      <c r="F38" s="11" t="n">
-        <v>710.6021842783916</v>
+      <c r="E38" s="4" t="n">
+        <v>1518.442352632967</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>779.7492844199003</v>
       </c>
       <c r="G38" s="4" t="n">
-        <v>108.5920565223662</v>
+        <v>-9.866244830037431</v>
       </c>
       <c r="H38" s="4" t="n">
-        <v>2894.152618893661</v>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>3046.750950095972</v>
+      </c>
+      <c r="I38" s="3" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
@@ -2448,16 +2684,16 @@
         <v>0</v>
       </c>
       <c r="E39" s="4" t="n">
-        <v>2398.388175033076</v>
+        <v>2417.291594174077</v>
       </c>
       <c r="F39" s="4" t="n">
-        <v>2817.323372105228</v>
+        <v>2733.901264750434</v>
       </c>
       <c r="G39" s="4" t="n">
-        <v>-3123.565634293172</v>
+        <v>-2941.154884736773</v>
       </c>
       <c r="H39" s="4" t="n">
-        <v>7920.341984359323</v>
+        <v>7775.738073084926</v>
       </c>
       <c r="I39" s="3" t="inlineStr"/>
     </row>
@@ -2481,16 +2717,16 @@
         <v>1</v>
       </c>
       <c r="E40" s="4" t="n">
-        <v>7571.776596941725</v>
+        <v>7585.986625820457</v>
       </c>
       <c r="F40" s="4" t="n">
-        <v>4822.643355110192</v>
+        <v>4817.471889472434</v>
       </c>
       <c r="G40" s="4" t="n">
-        <v>-1880.604379074251</v>
+        <v>-1856.258277545514</v>
       </c>
       <c r="H40" s="4" t="n">
-        <v>17024.1575729577</v>
+        <v>17028.23152918643</v>
       </c>
       <c r="I40" s="3" t="inlineStr"/>
     </row>
@@ -2514,16 +2750,16 @@
         <v>2</v>
       </c>
       <c r="E41" s="4" t="n">
-        <v>10777.23611063686</v>
+        <v>10786.1740690818</v>
       </c>
       <c r="F41" s="4" t="n">
-        <v>8697.019933832997</v>
+        <v>8292.902973302431</v>
       </c>
       <c r="G41" s="4" t="n">
-        <v>-6268.92295967581</v>
+        <v>-5467.915758590969</v>
       </c>
       <c r="H41" s="4" t="n">
-        <v>27823.39518094954</v>
+        <v>27040.26389675456</v>
       </c>
       <c r="I41" s="3" t="inlineStr"/>
     </row>
@@ -2547,16 +2783,16 @@
         <v>3</v>
       </c>
       <c r="E42" s="4" t="n">
-        <v>13022.24939431857</v>
+        <v>13033.7984442513</v>
       </c>
       <c r="F42" s="4" t="n">
-        <v>8994.806327366221</v>
+        <v>8753.581521603006</v>
       </c>
       <c r="G42" s="4" t="n">
-        <v>-4607.57100731922</v>
+        <v>-4123.221338090598</v>
       </c>
       <c r="H42" s="4" t="n">
-        <v>30652.06979595637</v>
+        <v>30190.81822659319</v>
       </c>
       <c r="I42" s="3" t="inlineStr"/>
     </row>
@@ -2580,16 +2816,16 @@
         <v>4</v>
       </c>
       <c r="E43" s="4" t="n">
-        <v>13741.07991358474</v>
+        <v>13755.90865015652</v>
       </c>
       <c r="F43" s="4" t="n">
-        <v>9352.866576469998</v>
+        <v>8979.139955154111</v>
       </c>
       <c r="G43" s="4" t="n">
-        <v>-4590.538576296454</v>
+        <v>-3843.205661945538</v>
       </c>
       <c r="H43" s="4" t="n">
-        <v>32072.69840346594</v>
+        <v>31355.02296225858</v>
       </c>
       <c r="I43" s="3" t="inlineStr"/>
     </row>
@@ -2613,16 +2849,16 @@
         <v>5</v>
       </c>
       <c r="E44" s="4" t="n">
-        <v>21725.70469725846</v>
+        <v>21763.49728730144</v>
       </c>
       <c r="F44" s="4" t="n">
-        <v>12898.78124107041</v>
+        <v>12455.47030093304</v>
       </c>
       <c r="G44" s="4" t="n">
-        <v>-3555.906535239537</v>
+        <v>-2649.224502527315</v>
       </c>
       <c r="H44" s="4" t="n">
-        <v>47007.31592975647</v>
+        <v>46176.21907713019</v>
       </c>
       <c r="I44" s="3" t="inlineStr"/>
     </row>
@@ -2646,16 +2882,16 @@
         <v>6</v>
       </c>
       <c r="E45" s="4" t="n">
-        <v>5057.280699423649</v>
+        <v>5211.520935475647</v>
       </c>
       <c r="F45" s="4" t="n">
-        <v>25176.40371280424</v>
+        <v>26769.6564451186</v>
       </c>
       <c r="G45" s="4" t="n">
-        <v>-44288.47057767265</v>
+        <v>-47257.0056969568</v>
       </c>
       <c r="H45" s="4" t="n">
-        <v>54403.03197651995</v>
+        <v>57680.04756790809</v>
       </c>
       <c r="I45" s="3" t="inlineStr"/>
     </row>
@@ -2678,19 +2914,19 @@
       <c r="D46" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="E46" s="11" t="n">
-        <v>-15679.00204063758</v>
-      </c>
-      <c r="F46" s="11" t="n">
-        <v>2747.878947462942</v>
+      <c r="E46" s="12" t="n">
+        <v>-15281.34723577393</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>2727.022121612675</v>
       </c>
       <c r="G46" s="4" t="n">
-        <v>-21064.84477766494</v>
+        <v>-20626.31059413477</v>
       </c>
       <c r="H46" s="4" t="n">
-        <v>-10293.15930361021</v>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
+        <v>-9936.383877413085</v>
+      </c>
+      <c r="I46" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -2715,19 +2951,23 @@
       <c r="D47" s="3" t="n">
         <v>-7</v>
       </c>
-      <c r="E47" s="4" t="n">
-        <v>-5415.2813608156</v>
-      </c>
-      <c r="F47" s="4" t="n">
-        <v>3650.1714436432</v>
+      <c r="E47" s="12" t="n">
+        <v>-2927.361702127672</v>
+      </c>
+      <c r="F47" s="12" t="n">
+        <v>1093.53323410042</v>
       </c>
       <c r="G47" s="4" t="n">
-        <v>-12569.61739035627</v>
+        <v>-5070.686840964496</v>
       </c>
       <c r="H47" s="4" t="n">
-        <v>1739.054668725073</v>
-      </c>
-      <c r="I47" s="3" t="inlineStr"/>
+        <v>-784.0365632908479</v>
+      </c>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
@@ -2749,16 +2989,16 @@
         <v>-6</v>
       </c>
       <c r="E48" s="4" t="n">
-        <v>-2155.025405681475</v>
+        <v>-960.6986008325601</v>
       </c>
       <c r="F48" s="4" t="n">
-        <v>2223.064060000318</v>
+        <v>2409.962831240294</v>
       </c>
       <c r="G48" s="4" t="n">
-        <v>-6512.230963282099</v>
+        <v>-5684.225750063537</v>
       </c>
       <c r="H48" s="4" t="n">
-        <v>2202.180151919149</v>
+        <v>3762.828548398416</v>
       </c>
       <c r="I48" s="3" t="inlineStr"/>
     </row>
@@ -2782,16 +3022,16 @@
         <v>-5</v>
       </c>
       <c r="E49" s="4" t="n">
-        <v>98.79696663296488</v>
+        <v>1658.442807549714</v>
       </c>
       <c r="F49" s="4" t="n">
-        <v>3600.761770696232</v>
+        <v>3066.867389435549</v>
       </c>
       <c r="G49" s="4" t="n">
-        <v>-6958.696103931651</v>
+        <v>-4352.617275743962</v>
       </c>
       <c r="H49" s="4" t="n">
-        <v>7156.29003719758</v>
+        <v>7669.502890843391</v>
       </c>
       <c r="I49" s="3" t="inlineStr"/>
     </row>
@@ -2815,16 +3055,16 @@
         <v>-4</v>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1715.973537262163</v>
+        <v>2905.731653012684</v>
       </c>
       <c r="F50" s="4" t="n">
-        <v>3330.253329255496</v>
+        <v>3491.245372354566</v>
       </c>
       <c r="G50" s="4" t="n">
-        <v>-4811.32298807861</v>
+        <v>-3937.109276802266</v>
       </c>
       <c r="H50" s="4" t="n">
-        <v>8243.270062602936</v>
+        <v>9748.572582827634</v>
       </c>
       <c r="I50" s="3" t="inlineStr"/>
     </row>
@@ -2848,16 +3088,16 @@
         <v>-3</v>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1895.068217568051</v>
+        <v>2495.321269990177</v>
       </c>
       <c r="F51" s="4" t="n">
-        <v>3972.644781658387</v>
+        <v>3999.994963447214</v>
       </c>
       <c r="G51" s="4" t="n">
-        <v>-5891.315554482387</v>
+        <v>-5344.668858366362</v>
       </c>
       <c r="H51" s="4" t="n">
-        <v>9681.45198961849</v>
+        <v>10335.31139834672</v>
       </c>
       <c r="I51" s="3" t="inlineStr"/>
     </row>
@@ -2881,16 +3121,16 @@
         <v>-2</v>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1787.757600479852</v>
+        <v>2231.517539766169</v>
       </c>
       <c r="F52" s="4" t="n">
-        <v>2079.308363575701</v>
+        <v>2032.852405782701</v>
       </c>
       <c r="G52" s="4" t="n">
-        <v>-2287.686792128522</v>
+        <v>-1752.873175567926</v>
       </c>
       <c r="H52" s="4" t="n">
-        <v>5863.201993088226</v>
+        <v>6215.908255100263</v>
       </c>
       <c r="I52" s="3" t="inlineStr"/>
     </row>
@@ -2914,16 +3154,16 @@
         <v>-1</v>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1892.266180296192</v>
+        <v>2040.659240978252</v>
       </c>
       <c r="F53" s="4" t="n">
-        <v>2388.936673477903</v>
+        <v>2334.104577335977</v>
       </c>
       <c r="G53" s="4" t="n">
-        <v>-2790.049699720497</v>
+        <v>-2534.185730600263</v>
       </c>
       <c r="H53" s="4" t="n">
-        <v>6574.582060312881</v>
+        <v>6615.504212556766</v>
       </c>
       <c r="I53" s="3" t="inlineStr"/>
     </row>
@@ -2947,16 +3187,16 @@
         <v>0</v>
       </c>
       <c r="E54" s="4" t="n">
-        <v>3881.688114616946</v>
+        <v>4026.373591485393</v>
       </c>
       <c r="F54" s="4" t="n">
-        <v>2166.991922353094</v>
+        <v>2178.110855582608</v>
       </c>
       <c r="G54" s="4" t="n">
-        <v>-365.6160531951186</v>
+        <v>-242.723685456519</v>
       </c>
       <c r="H54" s="4" t="n">
-        <v>8128.99228242901</v>
+        <v>8295.470868427306</v>
       </c>
       <c r="I54" s="3" t="inlineStr"/>
     </row>
@@ -2979,19 +3219,23 @@
       <c r="D55" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="E55" s="4" t="n">
-        <v>6173.883067328208</v>
-      </c>
-      <c r="F55" s="4" t="n">
-        <v>3204.583336967803</v>
+      <c r="E55" s="6" t="n">
+        <v>6343.117677398176</v>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>3189.39206688285</v>
       </c>
       <c r="G55" s="4" t="n">
-        <v>-107.1002731286853</v>
+        <v>91.90922630779096</v>
       </c>
       <c r="H55" s="4" t="n">
-        <v>12454.8664077851</v>
-      </c>
-      <c r="I55" s="3" t="inlineStr"/>
+        <v>12594.32612848856</v>
+      </c>
+      <c r="I55" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
@@ -3013,18 +3257,18 @@
         <v>2</v>
       </c>
       <c r="E56" s="6" t="n">
-        <v>7981.128457559306</v>
+        <v>8174.247217575693</v>
       </c>
       <c r="F56" s="6" t="n">
-        <v>3681.345888259722</v>
+        <v>3850.190727681354</v>
       </c>
       <c r="G56" s="4" t="n">
-        <v>765.6905165702519</v>
+        <v>627.8733913202404</v>
       </c>
       <c r="H56" s="4" t="n">
-        <v>15196.56639854836</v>
-      </c>
-      <c r="I56" s="13" t="inlineStr">
+        <v>15720.62104383115</v>
+      </c>
+      <c r="I56" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3050,18 +3294,18 @@
         <v>3</v>
       </c>
       <c r="E57" s="6" t="n">
-        <v>11721.96989973348</v>
+        <v>11976.4635827404</v>
       </c>
       <c r="F57" s="6" t="n">
-        <v>4680.889923713967</v>
+        <v>4885.742448381337</v>
       </c>
       <c r="G57" s="4" t="n">
-        <v>2547.425649254106</v>
+        <v>2400.408383912982</v>
       </c>
       <c r="H57" s="4" t="n">
-        <v>20896.51415021286</v>
-      </c>
-      <c r="I57" s="13" t="inlineStr">
+        <v>21552.51878156782</v>
+      </c>
+      <c r="I57" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3087,16 +3331,16 @@
         <v>4</v>
       </c>
       <c r="E58" s="4" t="n">
-        <v>17516.3746598453</v>
+        <v>17888.64620066591</v>
       </c>
       <c r="F58" s="4" t="n">
-        <v>9686.523475263839</v>
+        <v>9513.283231883066</v>
       </c>
       <c r="G58" s="4" t="n">
-        <v>-1469.211351671827</v>
+        <v>-757.3889338248955</v>
       </c>
       <c r="H58" s="4" t="n">
-        <v>36501.96067136242</v>
+        <v>36534.68133515673</v>
       </c>
       <c r="I58" s="3" t="inlineStr"/>
     </row>
@@ -3120,16 +3364,16 @@
         <v>5</v>
       </c>
       <c r="E59" s="4" t="n">
-        <v>33184.86520774037</v>
+        <v>33808.93589290079</v>
       </c>
       <c r="F59" s="4" t="n">
-        <v>20564.03561610122</v>
+        <v>20208.65150313544</v>
       </c>
       <c r="G59" s="4" t="n">
-        <v>-7120.644599818021</v>
+        <v>-5800.02105324468</v>
       </c>
       <c r="H59" s="4" t="n">
-        <v>73490.37501529875</v>
+        <v>73417.89283904625</v>
       </c>
       <c r="I59" s="3" t="inlineStr"/>
     </row>
@@ -3153,16 +3397,16 @@
         <v>6</v>
       </c>
       <c r="E60" s="4" t="n">
-        <v>27975.14207396546</v>
+        <v>29317.49588093638</v>
       </c>
       <c r="F60" s="4" t="n">
-        <v>14551.61766287981</v>
+        <v>16019.48377202944</v>
       </c>
       <c r="G60" s="4" t="n">
-        <v>-546.0285452789612</v>
+        <v>-2080.692312241317</v>
       </c>
       <c r="H60" s="4" t="n">
-        <v>56496.31269320989</v>
+        <v>60715.68407411408</v>
       </c>
       <c r="I60" s="3" t="inlineStr"/>
     </row>
@@ -3186,18 +3430,18 @@
         <v>7</v>
       </c>
       <c r="E61" s="6" t="n">
-        <v>54140.04461805554</v>
+        <v>56858.14775985662</v>
       </c>
       <c r="F61" s="6" t="n">
-        <v>8973.017020312665</v>
+        <v>9125.264611036053</v>
       </c>
       <c r="G61" s="4" t="n">
-        <v>36552.93125824271</v>
+        <v>38972.62912222596</v>
       </c>
       <c r="H61" s="4" t="n">
-        <v>71727.15797786837</v>
-      </c>
-      <c r="I61" s="13" t="inlineStr">
+        <v>74743.66639748728</v>
+      </c>
+      <c r="I61" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3223,16 +3467,16 @@
         <v>-7</v>
       </c>
       <c r="E62" s="4" t="n">
-        <v>-147.347960992908</v>
+        <v>121.4893617021277</v>
       </c>
       <c r="F62" s="4" t="n">
-        <v>400.6139444253572</v>
+        <v>201.098312504283</v>
       </c>
       <c r="G62" s="4" t="n">
-        <v>-932.5512920666082</v>
+        <v>-272.663330806267</v>
       </c>
       <c r="H62" s="4" t="n">
-        <v>637.8553700807921</v>
+        <v>515.6420542105225</v>
       </c>
       <c r="I62" s="3" t="inlineStr"/>
     </row>
@@ -3256,16 +3500,16 @@
         <v>-6</v>
       </c>
       <c r="E63" s="4" t="n">
-        <v>-415.7134404872031</v>
+        <v>-287.1504972247907</v>
       </c>
       <c r="F63" s="4" t="n">
-        <v>448.6297299577947</v>
+        <v>490.1223746997136</v>
       </c>
       <c r="G63" s="4" t="n">
-        <v>-1295.027711204481</v>
+        <v>-1247.790351636229</v>
       </c>
       <c r="H63" s="4" t="n">
-        <v>463.6008302300745</v>
+        <v>673.4893571866478</v>
       </c>
       <c r="I63" s="3" t="inlineStr"/>
     </row>
@@ -3289,16 +3533,16 @@
         <v>-5</v>
       </c>
       <c r="E64" s="4" t="n">
-        <v>265.0217239635992</v>
+        <v>433.2332844624203</v>
       </c>
       <c r="F64" s="4" t="n">
-        <v>480.6801306290973</v>
+        <v>483.2984170295607</v>
       </c>
       <c r="G64" s="4" t="n">
-        <v>-677.1113320694317</v>
+        <v>-514.0316129155185</v>
       </c>
       <c r="H64" s="4" t="n">
-        <v>1207.15477999663</v>
+        <v>1380.498181840359</v>
       </c>
       <c r="I64" s="3" t="inlineStr"/>
     </row>
@@ -3322,16 +3566,16 @@
         <v>-4</v>
       </c>
       <c r="E65" s="4" t="n">
-        <v>397.0246538054978</v>
+        <v>529.8593115750538</v>
       </c>
       <c r="F65" s="4" t="n">
-        <v>474.1810569195746</v>
+        <v>477.2921765047989</v>
       </c>
       <c r="G65" s="4" t="n">
-        <v>-532.3702177568684</v>
+        <v>-405.6333543743522</v>
       </c>
       <c r="H65" s="4" t="n">
-        <v>1326.419525367864</v>
+        <v>1465.35197752446</v>
       </c>
       <c r="I65" s="3" t="inlineStr"/>
     </row>
@@ -3355,16 +3599,16 @@
         <v>-3</v>
       </c>
       <c r="E66" s="4" t="n">
-        <v>95.92410403532442</v>
+        <v>157.1870756276251</v>
       </c>
       <c r="F66" s="4" t="n">
-        <v>451.1565951211592</v>
+        <v>437.0162062923402</v>
       </c>
       <c r="G66" s="4" t="n">
-        <v>-788.3428224021477</v>
+        <v>-699.3646887053617</v>
       </c>
       <c r="H66" s="4" t="n">
-        <v>980.1910304727965</v>
+        <v>1013.738839960612</v>
       </c>
       <c r="I66" s="3" t="inlineStr"/>
     </row>
@@ -3388,16 +3632,16 @@
         <v>-2</v>
       </c>
       <c r="E67" s="4" t="n">
-        <v>108.3014631503573</v>
+        <v>148.8217544533976</v>
       </c>
       <c r="F67" s="4" t="n">
-        <v>200.8043643978083</v>
+        <v>198.4720436151234</v>
       </c>
       <c r="G67" s="4" t="n">
-        <v>-285.2750910693468</v>
+        <v>-240.1834510322442</v>
       </c>
       <c r="H67" s="4" t="n">
-        <v>501.8780173700615</v>
+        <v>537.8269599390394</v>
       </c>
       <c r="I67" s="3" t="inlineStr"/>
     </row>
@@ -3421,16 +3665,16 @@
         <v>-1</v>
       </c>
       <c r="E68" s="4" t="n">
-        <v>70.1399686376607</v>
+        <v>80.54349455838759</v>
       </c>
       <c r="F68" s="4" t="n">
-        <v>336.0598740900538</v>
+        <v>351.5222888432189</v>
       </c>
       <c r="G68" s="4" t="n">
-        <v>-588.5373845788448</v>
+        <v>-608.4401915743215</v>
       </c>
       <c r="H68" s="4" t="n">
-        <v>728.8173218541662</v>
+        <v>769.5271806910966</v>
       </c>
       <c r="I68" s="3" t="inlineStr"/>
     </row>
@@ -3454,16 +3698,16 @@
         <v>0</v>
       </c>
       <c r="E69" s="4" t="n">
-        <v>198.6868253105739</v>
+        <v>207.7311153609667</v>
       </c>
       <c r="F69" s="4" t="n">
-        <v>208.924727367532</v>
+        <v>198.5404587670319</v>
       </c>
       <c r="G69" s="4" t="n">
-        <v>-210.8056403297888</v>
+        <v>-181.4081838224159</v>
       </c>
       <c r="H69" s="4" t="n">
-        <v>608.1792909509365</v>
+        <v>596.8704145443494</v>
       </c>
       <c r="I69" s="3" t="inlineStr"/>
     </row>
@@ -3487,16 +3731,16 @@
         <v>1</v>
       </c>
       <c r="E70" s="4" t="n">
-        <v>308.7693352275162</v>
+        <v>315.4158556770799</v>
       </c>
       <c r="F70" s="4" t="n">
-        <v>795.2467307641839</v>
+        <v>812.2370529759227</v>
       </c>
       <c r="G70" s="4" t="n">
-        <v>-1249.914257070284</v>
+        <v>-1276.568768155729</v>
       </c>
       <c r="H70" s="4" t="n">
-        <v>1867.452927525317</v>
+        <v>1907.400479509888</v>
       </c>
       <c r="I70" s="3" t="inlineStr"/>
     </row>
@@ -3520,16 +3764,16 @@
         <v>2</v>
       </c>
       <c r="E71" s="4" t="n">
-        <v>637.4837316720175</v>
+        <v>642.8994349101745</v>
       </c>
       <c r="F71" s="4" t="n">
-        <v>1270.496584603844</v>
+        <v>1251.140143136769</v>
       </c>
       <c r="G71" s="4" t="n">
-        <v>-1852.689574151517</v>
+        <v>-1809.335245637892</v>
       </c>
       <c r="H71" s="4" t="n">
-        <v>3127.657037495552</v>
+        <v>3095.134115458241</v>
       </c>
       <c r="I71" s="3" t="inlineStr"/>
     </row>
@@ -3553,16 +3797,16 @@
         <v>3</v>
       </c>
       <c r="E72" s="4" t="n">
-        <v>794.4208963857735</v>
+        <v>802.2652138708379</v>
       </c>
       <c r="F72" s="4" t="n">
-        <v>887.2122332447949</v>
+        <v>874.1577863077837</v>
       </c>
       <c r="G72" s="4" t="n">
-        <v>-944.5150807740246</v>
+        <v>-911.0840472924181</v>
       </c>
       <c r="H72" s="4" t="n">
-        <v>2533.356873545571</v>
+        <v>2515.614475034094</v>
       </c>
       <c r="I72" s="3" t="inlineStr"/>
     </row>
@@ -3586,18 +3830,18 @@
         <v>4</v>
       </c>
       <c r="E73" s="6" t="n">
-        <v>1602.270465811529</v>
+        <v>1618.925816379521</v>
       </c>
       <c r="F73" s="6" t="n">
-        <v>704.8898569966788</v>
+        <v>700.2253585573289</v>
       </c>
       <c r="G73" s="4" t="n">
-        <v>220.6863460980383</v>
+        <v>246.4841136071559</v>
       </c>
       <c r="H73" s="4" t="n">
-        <v>2983.854585525019</v>
-      </c>
-      <c r="I73" s="13" t="inlineStr">
+        <v>2991.367519151886</v>
+      </c>
+      <c r="I73" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3623,18 +3867,18 @@
         <v>5</v>
       </c>
       <c r="E74" s="6" t="n">
-        <v>4356.939015456991</v>
+        <v>4400.07479349951</v>
       </c>
       <c r="F74" s="6" t="n">
-        <v>1997.687637292517</v>
+        <v>2091.276628927239</v>
       </c>
       <c r="G74" s="4" t="n">
-        <v>441.4712463636583</v>
+        <v>301.1726008021224</v>
       </c>
       <c r="H74" s="4" t="n">
-        <v>8272.406784550323</v>
-      </c>
-      <c r="I74" s="13" t="inlineStr">
+        <v>8498.976986196896</v>
+      </c>
+      <c r="I74" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3660,18 +3904,18 @@
         <v>6</v>
       </c>
       <c r="E75" s="6" t="n">
-        <v>3866.547576572173</v>
+        <v>3982.895214493728</v>
       </c>
       <c r="F75" s="6" t="n">
-        <v>597.2517547432753</v>
+        <v>575.4098744125489</v>
       </c>
       <c r="G75" s="4" t="n">
-        <v>2695.934137275353</v>
+        <v>2855.091860645132</v>
       </c>
       <c r="H75" s="4" t="n">
-        <v>5037.161015868993</v>
-      </c>
-      <c r="I75" s="13" t="inlineStr">
+        <v>5110.698568342324</v>
+      </c>
+      <c r="I75" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3697,18 +3941,18 @@
         <v>7</v>
       </c>
       <c r="E76" s="6" t="n">
-        <v>4566.593923611112</v>
+        <v>4833.089068100358</v>
       </c>
       <c r="F76" s="6" t="n">
-        <v>810.1679978534079</v>
+        <v>681.5233503311392</v>
       </c>
       <c r="G76" s="4" t="n">
-        <v>2978.664647818432</v>
+        <v>3497.303301451326</v>
       </c>
       <c r="H76" s="4" t="n">
-        <v>6154.523199403791</v>
-      </c>
-      <c r="I76" s="13" t="inlineStr">
+        <v>6168.874834749391</v>
+      </c>
+      <c r="I76" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3733,19 +3977,23 @@
       <c r="D77" s="3" t="n">
         <v>-7</v>
       </c>
-      <c r="E77" s="4" t="n">
-        <v>-1885.235704787233</v>
-      </c>
-      <c r="F77" s="4" t="n">
-        <v>1162.233300592607</v>
+      <c r="E77" s="12" t="n">
+        <v>-1076.361702127659</v>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>321.7377691220364</v>
       </c>
       <c r="G77" s="4" t="n">
-        <v>-4163.212973948743</v>
+        <v>-1706.96772960685</v>
       </c>
       <c r="H77" s="4" t="n">
-        <v>392.7415643742772</v>
-      </c>
-      <c r="I77" s="3" t="inlineStr"/>
+        <v>-445.7556746484677</v>
+      </c>
+      <c r="I77" s="13" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="inlineStr">
@@ -3766,19 +4014,19 @@
       <c r="D78" s="3" t="n">
         <v>-6</v>
       </c>
-      <c r="E78" s="11" t="n">
-        <v>-1671.084836571076</v>
-      </c>
-      <c r="F78" s="11" t="n">
-        <v>800.8410558266824</v>
+      <c r="E78" s="12" t="n">
+        <v>-1283.099040240515</v>
+      </c>
+      <c r="F78" s="12" t="n">
+        <v>404.1032064500932</v>
       </c>
       <c r="G78" s="4" t="n">
-        <v>-3240.733305991374</v>
+        <v>-2075.141324882698</v>
       </c>
       <c r="H78" s="4" t="n">
-        <v>-101.4363671507788</v>
-      </c>
-      <c r="I78" s="12" t="inlineStr">
+        <v>-491.0567555983325</v>
+      </c>
+      <c r="I78" s="13" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -3804,16 +4052,16 @@
         <v>-5</v>
       </c>
       <c r="E79" s="4" t="n">
-        <v>-821.5510161779566</v>
+        <v>-319.3396747556434</v>
       </c>
       <c r="F79" s="4" t="n">
-        <v>843.8865322389372</v>
+        <v>532.4448549887126</v>
       </c>
       <c r="G79" s="4" t="n">
-        <v>-2475.568619366273</v>
+        <v>-1362.93159053352</v>
       </c>
       <c r="H79" s="4" t="n">
-        <v>832.4665870103602</v>
+        <v>724.2522410222333</v>
       </c>
       <c r="I79" s="3" t="inlineStr"/>
     </row>
@@ -3837,16 +4085,16 @@
         <v>-4</v>
       </c>
       <c r="E80" s="4" t="n">
-        <v>379.4009302325578</v>
+        <v>745.1695163847744</v>
       </c>
       <c r="F80" s="4" t="n">
-        <v>989.2145817232554</v>
+        <v>1017.510520942237</v>
       </c>
       <c r="G80" s="4" t="n">
-        <v>-1559.459649945023</v>
+        <v>-1249.15110466201</v>
       </c>
       <c r="H80" s="4" t="n">
-        <v>2318.261510410138</v>
+        <v>2739.490137431559</v>
       </c>
       <c r="I80" s="3" t="inlineStr"/>
     </row>
@@ -3870,16 +4118,16 @@
         <v>-3</v>
       </c>
       <c r="E81" s="4" t="n">
-        <v>254.5530185063297</v>
+        <v>442.8881259492551</v>
       </c>
       <c r="F81" s="4" t="n">
-        <v>762.2148032088357</v>
+        <v>782.4833555646408</v>
       </c>
       <c r="G81" s="4" t="n">
-        <v>-1239.387995782988</v>
+        <v>-1090.779250957441</v>
       </c>
       <c r="H81" s="4" t="n">
-        <v>1748.494032795648</v>
+        <v>1976.555502855951</v>
       </c>
       <c r="I81" s="3" t="inlineStr"/>
     </row>
@@ -3903,16 +4151,16 @@
         <v>-2</v>
       </c>
       <c r="E82" s="4" t="n">
-        <v>1237.20611941039</v>
+        <v>1369.655904582055</v>
       </c>
       <c r="F82" s="4" t="n">
-        <v>1195.226996795451</v>
+        <v>1236.286361915298</v>
       </c>
       <c r="G82" s="4" t="n">
-        <v>-1105.438794308693</v>
+        <v>-1053.465364771929</v>
       </c>
       <c r="H82" s="4" t="n">
-        <v>3579.851033129473</v>
+        <v>3792.77717393604</v>
       </c>
       <c r="I82" s="3" t="inlineStr"/>
     </row>
@@ -3936,16 +4184,16 @@
         <v>-1</v>
       </c>
       <c r="E83" s="4" t="n">
-        <v>1104.301286372003</v>
+        <v>1136.720505454728</v>
       </c>
       <c r="F83" s="4" t="n">
-        <v>981.2000095915067</v>
+        <v>957.2995822210676</v>
       </c>
       <c r="G83" s="4" t="n">
-        <v>-818.8507324273498</v>
+        <v>-739.5866756985642</v>
       </c>
       <c r="H83" s="4" t="n">
-        <v>3027.453305171356</v>
+        <v>3013.027686608021</v>
       </c>
       <c r="I83" s="3" t="inlineStr"/>
     </row>
@@ -3969,16 +4217,16 @@
         <v>0</v>
       </c>
       <c r="E84" s="4" t="n">
-        <v>965.3154410107055</v>
+        <v>1011.274729991285</v>
       </c>
       <c r="F84" s="4" t="n">
-        <v>871.9425265468357</v>
+        <v>917.789711621054</v>
       </c>
       <c r="G84" s="4" t="n">
-        <v>-743.6919110210923</v>
+        <v>-787.5931047859812</v>
       </c>
       <c r="H84" s="4" t="n">
-        <v>2674.322793042503</v>
+        <v>2810.142564768551</v>
       </c>
       <c r="I84" s="3" t="inlineStr"/>
     </row>
@@ -4002,16 +4250,16 @@
         <v>1</v>
       </c>
       <c r="E85" s="4" t="n">
-        <v>1955.334725728282</v>
+        <v>2012.757734537367</v>
       </c>
       <c r="F85" s="4" t="n">
-        <v>1417.840547728037</v>
+        <v>1378.703606886917</v>
       </c>
       <c r="G85" s="4" t="n">
-        <v>-823.6327478186704</v>
+        <v>-689.5013349609899</v>
       </c>
       <c r="H85" s="4" t="n">
-        <v>4734.302199275234</v>
+        <v>4715.016804035723</v>
       </c>
       <c r="I85" s="3" t="inlineStr"/>
     </row>
@@ -4035,16 +4283,16 @@
         <v>2</v>
       </c>
       <c r="E86" s="4" t="n">
-        <v>2589.999323104022</v>
+        <v>2667.481192886586</v>
       </c>
       <c r="F86" s="4" t="n">
-        <v>3262.012090845298</v>
+        <v>3268.241077074551</v>
       </c>
       <c r="G86" s="4" t="n">
-        <v>-3803.544374952763</v>
+        <v>-3738.271318179533</v>
       </c>
       <c r="H86" s="4" t="n">
-        <v>8983.543021160807</v>
+        <v>9073.233703952705</v>
       </c>
       <c r="I86" s="3" t="inlineStr"/>
     </row>
@@ -4068,16 +4316,16 @@
         <v>3</v>
       </c>
       <c r="E87" s="4" t="n">
-        <v>5895.464574958789</v>
+        <v>5994.467580735334</v>
       </c>
       <c r="F87" s="4" t="n">
-        <v>8034.36730084834</v>
+        <v>8019.588228743292</v>
       </c>
       <c r="G87" s="4" t="n">
-        <v>-9851.895334703957</v>
+        <v>-9723.925347601518</v>
       </c>
       <c r="H87" s="4" t="n">
-        <v>21642.82448462153</v>
+        <v>21712.86050907219</v>
       </c>
       <c r="I87" s="3" t="inlineStr"/>
     </row>
@@ -4101,16 +4349,16 @@
         <v>4</v>
       </c>
       <c r="E88" s="4" t="n">
-        <v>14005.99557330883</v>
+        <v>14112.08590612526</v>
       </c>
       <c r="F88" s="4" t="n">
-        <v>14242.98173818311</v>
+        <v>13656.55190314401</v>
       </c>
       <c r="G88" s="4" t="n">
-        <v>-13910.24863353005</v>
+        <v>-12654.755824037</v>
       </c>
       <c r="H88" s="4" t="n">
-        <v>41922.23978014771</v>
+        <v>40878.92763628752</v>
       </c>
       <c r="I88" s="3" t="inlineStr"/>
     </row>
@@ -4134,16 +4382,16 @@
         <v>5</v>
       </c>
       <c r="E89" s="4" t="n">
-        <v>24428.65920995414</v>
+        <v>24602.45493615591</v>
       </c>
       <c r="F89" s="4" t="n">
-        <v>20779.7233200739</v>
+        <v>21018.52850660525</v>
       </c>
       <c r="G89" s="4" t="n">
-        <v>-16299.5984973907</v>
+        <v>-16593.86093679038</v>
       </c>
       <c r="H89" s="4" t="n">
-        <v>65156.91691729899</v>
+        <v>65798.77080910219</v>
       </c>
       <c r="I89" s="3" t="inlineStr"/>
     </row>
@@ -4167,18 +4415,18 @@
         <v>6</v>
       </c>
       <c r="E90" s="6" t="n">
-        <v>13414.00521342458</v>
+        <v>13810.91239359319</v>
       </c>
       <c r="F90" s="6" t="n">
-        <v>4215.717606836577</v>
+        <v>4551.836538066293</v>
       </c>
       <c r="G90" s="4" t="n">
-        <v>5151.198704024893</v>
+        <v>4889.31277898326</v>
       </c>
       <c r="H90" s="4" t="n">
-        <v>21676.81172282427</v>
-      </c>
-      <c r="I90" s="13" t="inlineStr">
+        <v>22732.51200820313</v>
+      </c>
+      <c r="I90" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4204,18 +4452,18 @@
         <v>7</v>
       </c>
       <c r="E91" s="6" t="n">
-        <v>20263.48611111111</v>
+        <v>21086.35250896057</v>
       </c>
       <c r="F91" s="6" t="n">
-        <v>2653.716746399814</v>
+        <v>2590.697666698343</v>
       </c>
       <c r="G91" s="4" t="n">
-        <v>15062.20128816747</v>
+        <v>16008.58508223182</v>
       </c>
       <c r="H91" s="4" t="n">
-        <v>25464.77093405474</v>
-      </c>
-      <c r="I91" s="13" t="inlineStr">
+        <v>26164.11993568932</v>
+      </c>
+      <c r="I91" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4241,16 +4489,16 @@
         <v>-7</v>
       </c>
       <c r="E92" s="4" t="n">
-        <v>385.2353266888174</v>
+        <v>509.4404761904766</v>
       </c>
       <c r="F92" s="4" t="n">
-        <v>743.1475900232177</v>
+        <v>761.154027055137</v>
       </c>
       <c r="G92" s="4" t="n">
-        <v>-1071.333949756689</v>
+        <v>-982.421416837592</v>
       </c>
       <c r="H92" s="4" t="n">
-        <v>1841.804603134324</v>
+        <v>2001.302369218545</v>
       </c>
       <c r="I92" s="3" t="inlineStr"/>
     </row>
@@ -4274,16 +4522,16 @@
         <v>-6</v>
       </c>
       <c r="E93" s="4" t="n">
-        <v>589.7136398576183</v>
+        <v>598.8938643292664</v>
       </c>
       <c r="F93" s="4" t="n">
-        <v>738.1032280950394</v>
+        <v>739.7584846975616</v>
       </c>
       <c r="G93" s="4" t="n">
-        <v>-856.9686872086588</v>
+        <v>-851.0327656779542</v>
       </c>
       <c r="H93" s="4" t="n">
-        <v>2036.395966923895</v>
+        <v>2048.820494336487</v>
       </c>
       <c r="I93" s="3" t="inlineStr"/>
     </row>
@@ -4307,16 +4555,16 @@
         <v>-5</v>
       </c>
       <c r="E94" s="4" t="n">
-        <v>566.8929793164293</v>
+        <v>574.7449935973216</v>
       </c>
       <c r="F94" s="4" t="n">
-        <v>415.7263512877529</v>
+        <v>432.7694417047523</v>
       </c>
       <c r="G94" s="4" t="n">
-        <v>-247.9306692075664</v>
+        <v>-273.4831121439929</v>
       </c>
       <c r="H94" s="4" t="n">
-        <v>1381.716627840425</v>
+        <v>1422.973099338636</v>
       </c>
       <c r="I94" s="3" t="inlineStr"/>
     </row>
@@ -4340,16 +4588,16 @@
         <v>-4</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>195.6878068815421</v>
+        <v>203.2172414623824</v>
       </c>
       <c r="F95" s="4" t="n">
-        <v>306.3831543393309</v>
+        <v>298.6201326378863</v>
       </c>
       <c r="G95" s="4" t="n">
-        <v>-404.8231756235463</v>
+        <v>-382.0782185078746</v>
       </c>
       <c r="H95" s="4" t="n">
-        <v>796.1987893866306</v>
+        <v>788.5127014326395</v>
       </c>
       <c r="I95" s="3" t="inlineStr"/>
     </row>
@@ -4373,16 +4621,16 @@
         <v>-3</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>146.4536421742002</v>
+        <v>154.5422557037322</v>
       </c>
       <c r="F96" s="4" t="n">
-        <v>257.1184961141852</v>
+        <v>260.3201553658078</v>
       </c>
       <c r="G96" s="4" t="n">
-        <v>-357.4986102096028</v>
+        <v>-355.6852488132511</v>
       </c>
       <c r="H96" s="4" t="n">
-        <v>650.4058945580031</v>
+        <v>664.7697602207155</v>
       </c>
       <c r="I96" s="3" t="inlineStr"/>
     </row>
@@ -4406,16 +4654,16 @@
         <v>-2</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>1443.161731762176</v>
+        <v>1450.413738097645</v>
       </c>
       <c r="F97" s="4" t="n">
-        <v>1523.107250262089</v>
+        <v>1575.03587124915</v>
       </c>
       <c r="G97" s="4" t="n">
-        <v>-1542.128478751517</v>
+        <v>-1636.656569550689</v>
       </c>
       <c r="H97" s="4" t="n">
-        <v>4428.45194227587</v>
+        <v>4537.48404574598</v>
       </c>
       <c r="I97" s="3" t="inlineStr"/>
     </row>
@@ -4439,16 +4687,16 @@
         <v>-1</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>948.7782395886342</v>
+        <v>957.0721456468941</v>
       </c>
       <c r="F98" s="4" t="n">
-        <v>909.4051296227253</v>
+        <v>867.4498305065248</v>
       </c>
       <c r="G98" s="4" t="n">
-        <v>-833.6558144719075</v>
+        <v>-743.1295221458945</v>
       </c>
       <c r="H98" s="4" t="n">
-        <v>2731.212293649176</v>
+        <v>2657.273813439683</v>
       </c>
       <c r="I98" s="3" t="inlineStr"/>
     </row>
@@ -4472,16 +4720,16 @@
         <v>0</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>-252.5642920549703</v>
+        <v>-253.747123542041</v>
       </c>
       <c r="F99" s="4" t="n">
-        <v>508.483056386178</v>
+        <v>489.2790071981515</v>
       </c>
       <c r="G99" s="4" t="n">
-        <v>-1249.191082571879</v>
+        <v>-1212.733977650418</v>
       </c>
       <c r="H99" s="4" t="n">
-        <v>744.0624984619386</v>
+        <v>705.239730566336</v>
       </c>
       <c r="I99" s="3" t="inlineStr"/>
     </row>
@@ -4505,18 +4753,18 @@
         <v>1</v>
       </c>
       <c r="E100" s="6" t="n">
-        <v>1888.112415659674</v>
+        <v>1882.894566743057</v>
       </c>
       <c r="F100" s="6" t="n">
-        <v>769.3467669916794</v>
+        <v>750.3190342716441</v>
       </c>
       <c r="G100" s="4" t="n">
-        <v>380.1927523559821</v>
+        <v>412.2692595706346</v>
       </c>
       <c r="H100" s="4" t="n">
-        <v>3396.032078963365</v>
-      </c>
-      <c r="I100" s="13" t="inlineStr">
+        <v>3353.519873915479</v>
+      </c>
+      <c r="I100" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4542,18 +4790,18 @@
         <v>2</v>
       </c>
       <c r="E101" s="6" t="n">
-        <v>2396.645152259267</v>
+        <v>2388.675166018118</v>
       </c>
       <c r="F101" s="6" t="n">
-        <v>815.0948251366245</v>
+        <v>773.5824121225621</v>
       </c>
       <c r="G101" s="4" t="n">
-        <v>799.0592949914828</v>
+        <v>872.4536382578963</v>
       </c>
       <c r="H101" s="4" t="n">
-        <v>3994.231009527051</v>
-      </c>
-      <c r="I101" s="13" t="inlineStr">
+        <v>3904.89669377834</v>
+      </c>
+      <c r="I101" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4579,16 +4827,16 @@
         <v>3</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>3377.671985532234</v>
+        <v>3366.787593228801</v>
       </c>
       <c r="F102" s="4" t="n">
-        <v>2015.73774190769</v>
+        <v>2052.047053144947</v>
       </c>
       <c r="G102" s="4" t="n">
-        <v>-573.1739886068385</v>
+        <v>-655.224630935295</v>
       </c>
       <c r="H102" s="4" t="n">
-        <v>7328.517959671308</v>
+        <v>7388.799817392896</v>
       </c>
       <c r="I102" s="3" t="inlineStr"/>
     </row>
@@ -4611,19 +4859,23 @@
       <c r="D103" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E103" s="4" t="n">
-        <v>4975.695735035852</v>
-      </c>
-      <c r="F103" s="4" t="n">
-        <v>2858.563869332089</v>
+      <c r="E103" s="6" t="n">
+        <v>4961.4512264114</v>
+      </c>
+      <c r="F103" s="6" t="n">
+        <v>2420.789026187752</v>
       </c>
       <c r="G103" s="4" t="n">
-        <v>-627.089448855043</v>
+        <v>216.7047350834064</v>
       </c>
       <c r="H103" s="4" t="n">
-        <v>10578.48091892675</v>
-      </c>
-      <c r="I103" s="3" t="inlineStr"/>
+        <v>9706.197717739393</v>
+      </c>
+      <c r="I103" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="3" t="inlineStr">
@@ -4645,18 +4897,18 @@
         <v>5</v>
       </c>
       <c r="E104" s="6" t="n">
-        <v>7767.498500369138</v>
+        <v>7749.27259366925</v>
       </c>
       <c r="F104" s="6" t="n">
-        <v>2203.596605376687</v>
+        <v>2717.404591032709</v>
       </c>
       <c r="G104" s="4" t="n">
-        <v>3448.449153830833</v>
+        <v>2423.15959524514</v>
       </c>
       <c r="H104" s="4" t="n">
-        <v>12086.54784690744</v>
-      </c>
-      <c r="I104" s="13" t="inlineStr">
+        <v>13075.38559209336</v>
+      </c>
+      <c r="I104" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4682,18 +4934,18 @@
         <v>6</v>
       </c>
       <c r="E105" s="6" t="n">
-        <v>6619.965277777777</v>
+        <v>6595.550793650796</v>
       </c>
       <c r="F105" s="6" t="n">
-        <v>586.7384061659094</v>
+        <v>609.0009331228244</v>
       </c>
       <c r="G105" s="4" t="n">
-        <v>5469.958001692595</v>
+        <v>5401.90896473006</v>
       </c>
       <c r="H105" s="4" t="n">
-        <v>7769.97255386296</v>
-      </c>
-      <c r="I105" s="13" t="inlineStr">
+        <v>7789.192622571532</v>
+      </c>
+      <c r="I105" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -4719,16 +4971,16 @@
         <v>-7</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>285.6537501032847</v>
+        <v>373.0023033502937</v>
       </c>
       <c r="F106" s="4" t="n">
-        <v>552.892860564104</v>
+        <v>578.7851833080362</v>
       </c>
       <c r="G106" s="4" t="n">
-        <v>-798.0162566023591</v>
+        <v>-761.4166559334572</v>
       </c>
       <c r="H106" s="4" t="n">
-        <v>1369.323756808928</v>
+        <v>1507.421262634045</v>
       </c>
       <c r="I106" s="3" t="inlineStr"/>
     </row>
@@ -4752,16 +5004,16 @@
         <v>-6</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>431.6477286106806</v>
+        <v>438.4862630832869</v>
       </c>
       <c r="F107" s="4" t="n">
-        <v>553.9730248416804</v>
+        <v>563.2902508991332</v>
       </c>
       <c r="G107" s="4" t="n">
-        <v>-654.1394000790131</v>
+        <v>-665.5626286790142</v>
       </c>
       <c r="H107" s="4" t="n">
-        <v>1517.434857300374</v>
+        <v>1542.535154845588</v>
       </c>
       <c r="I107" s="3" t="inlineStr"/>
     </row>
@@ -4785,16 +5037,16 @@
         <v>-5</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>420.775428248567</v>
+        <v>426.792054017921</v>
       </c>
       <c r="F108" s="4" t="n">
-        <v>287.7061915837705</v>
+        <v>323.6975007234823</v>
       </c>
       <c r="G108" s="4" t="n">
-        <v>-143.1287072556232</v>
+        <v>-207.6550474001042</v>
       </c>
       <c r="H108" s="4" t="n">
-        <v>984.6795637527573</v>
+        <v>1061.239155435946</v>
       </c>
       <c r="I108" s="3" t="inlineStr"/>
     </row>
@@ -4818,16 +5070,16 @@
         <v>-4</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>146.0709047003967</v>
+        <v>151.5867039355543</v>
       </c>
       <c r="F109" s="4" t="n">
-        <v>236.4153843662093</v>
+        <v>227.2433422971223</v>
       </c>
       <c r="G109" s="4" t="n">
-        <v>-317.3032486573734</v>
+        <v>-293.8102469668055</v>
       </c>
       <c r="H109" s="4" t="n">
-        <v>609.4450580581669</v>
+        <v>596.9836548379141</v>
       </c>
       <c r="I109" s="3" t="inlineStr"/>
     </row>
@@ -4851,16 +5103,16 @@
         <v>-3</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>110.8433519167631</v>
+        <v>116.4239305450163</v>
       </c>
       <c r="F110" s="4" t="n">
-        <v>180.9462605237642</v>
+        <v>175.4456704713854</v>
       </c>
       <c r="G110" s="4" t="n">
-        <v>-243.8113187098147</v>
+        <v>-227.4495835788991</v>
       </c>
       <c r="H110" s="4" t="n">
-        <v>465.4980225433408</v>
+        <v>460.2974446689317</v>
       </c>
       <c r="I110" s="3" t="inlineStr"/>
     </row>
@@ -4884,16 +5136,16 @@
         <v>-2</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>1071.068814352604</v>
+        <v>1075.781280919428</v>
       </c>
       <c r="F111" s="4" t="n">
-        <v>1199.599099574423</v>
+        <v>1184.608954929783</v>
       </c>
       <c r="G111" s="4" t="n">
-        <v>-1280.145420813266</v>
+        <v>-1246.052270742946</v>
       </c>
       <c r="H111" s="4" t="n">
-        <v>3422.283049518474</v>
+        <v>3397.614832581803</v>
       </c>
       <c r="I111" s="3" t="inlineStr"/>
     </row>
@@ -4917,16 +5169,16 @@
         <v>-1</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>725.3202433594715</v>
+        <v>731.1275810429223</v>
       </c>
       <c r="F112" s="4" t="n">
-        <v>698.1995353472498</v>
+        <v>659.4694923044651</v>
       </c>
       <c r="G112" s="4" t="n">
-        <v>-643.1508459211382</v>
+        <v>-561.4326238738294</v>
       </c>
       <c r="H112" s="4" t="n">
-        <v>2093.791332640081</v>
+        <v>2023.687785959674</v>
       </c>
       <c r="I112" s="3" t="inlineStr"/>
     </row>
@@ -4950,16 +5202,16 @@
         <v>0</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>-170.2884977006686</v>
+        <v>-170.9936675756291</v>
       </c>
       <c r="F113" s="4" t="n">
-        <v>366.708317319381</v>
+        <v>373.272542260897</v>
       </c>
       <c r="G113" s="4" t="n">
-        <v>-889.0367996466554</v>
+        <v>-902.6078504069872</v>
       </c>
       <c r="H113" s="4" t="n">
-        <v>548.4598042453182</v>
+        <v>560.6205152557288</v>
       </c>
       <c r="I113" s="3" t="inlineStr"/>
     </row>
@@ -4983,18 +5235,18 @@
         <v>1</v>
       </c>
       <c r="E114" s="6" t="n">
-        <v>1434.83626841344</v>
+        <v>1431.134617991675</v>
       </c>
       <c r="F114" s="6" t="n">
-        <v>596.1221793622266</v>
+        <v>613.7869616214251</v>
       </c>
       <c r="G114" s="4" t="n">
-        <v>266.4367968634756</v>
+        <v>228.1121732136821</v>
       </c>
       <c r="H114" s="4" t="n">
-        <v>2603.235739963404</v>
-      </c>
-      <c r="I114" s="13" t="inlineStr">
+        <v>2634.157062769669</v>
+      </c>
+      <c r="I114" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5020,18 +5272,18 @@
         <v>2</v>
       </c>
       <c r="E115" s="6" t="n">
-        <v>1812.2012056202</v>
+        <v>1806.368091629098</v>
       </c>
       <c r="F115" s="6" t="n">
-        <v>652.9386442608961</v>
+        <v>611.5451649521649</v>
       </c>
       <c r="G115" s="4" t="n">
-        <v>532.4414628688435</v>
+        <v>607.7395683228544</v>
       </c>
       <c r="H115" s="4" t="n">
-        <v>3091.960948371556</v>
-      </c>
-      <c r="I115" s="13" t="inlineStr">
+        <v>3004.99661493534</v>
+      </c>
+      <c r="I115" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5057,16 +5309,16 @@
         <v>3</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>2487.806412981174</v>
+        <v>2479.783946902251</v>
       </c>
       <c r="F116" s="4" t="n">
-        <v>1435.847072567536</v>
+        <v>1493.675246760874</v>
       </c>
       <c r="G116" s="4" t="n">
-        <v>-326.4538492511961</v>
+        <v>-447.8195367490616</v>
       </c>
       <c r="H116" s="4" t="n">
-        <v>5302.066675213544</v>
+        <v>5407.387430553564</v>
       </c>
       <c r="I116" s="3" t="inlineStr"/>
     </row>
@@ -5089,19 +5341,23 @@
       <c r="D117" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="E117" s="4" t="n">
-        <v>3790.543591450753</v>
-      </c>
-      <c r="F117" s="4" t="n">
-        <v>1957.953746379589</v>
+      <c r="E117" s="6" t="n">
+        <v>3780.152280643041</v>
+      </c>
+      <c r="F117" s="6" t="n">
+        <v>1646.020642512038</v>
       </c>
       <c r="G117" s="4" t="n">
-        <v>-47.04575145324179</v>
+        <v>553.9518213194469</v>
       </c>
       <c r="H117" s="4" t="n">
-        <v>7628.132934354747</v>
-      </c>
-      <c r="I117" s="3" t="inlineStr"/>
+        <v>7006.352739966635</v>
+      </c>
+      <c r="I117" s="14" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="inlineStr">
@@ -5123,18 +5379,18 @@
         <v>5</v>
       </c>
       <c r="E118" s="6" t="n">
-        <v>5909.873884574686</v>
+        <v>5896.969872531055</v>
       </c>
       <c r="F118" s="6" t="n">
-        <v>1587.155871319375</v>
+        <v>1766.606747039971</v>
       </c>
       <c r="G118" s="4" t="n">
-        <v>2799.048376788711</v>
+        <v>2434.420648332713</v>
       </c>
       <c r="H118" s="4" t="n">
-        <v>9020.699392360661</v>
-      </c>
-      <c r="I118" s="13" t="inlineStr">
+        <v>9359.519096729398</v>
+      </c>
+      <c r="I118" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5160,18 +5416,18 @@
         <v>6</v>
       </c>
       <c r="E119" s="6" t="n">
-        <v>5291.34601525855</v>
+        <v>5274.420951544332</v>
       </c>
       <c r="F119" s="6" t="n">
-        <v>455.1059709913194</v>
+        <v>451.1112228720416</v>
       </c>
       <c r="G119" s="4" t="n">
-        <v>4399.338312115564</v>
+        <v>4390.242954715131</v>
       </c>
       <c r="H119" s="4" t="n">
-        <v>6183.353718401537</v>
-      </c>
-      <c r="I119" s="13" t="inlineStr">
+        <v>6158.598948373533</v>
+      </c>
+      <c r="I119" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5197,16 +5453,16 @@
         <v>-7</v>
       </c>
       <c r="E120" s="4" t="n">
-        <v>1626.982551672152</v>
+        <v>2097.946412280941</v>
       </c>
       <c r="F120" s="4" t="n">
-        <v>3201.437569277318</v>
+        <v>3260.308546313539</v>
       </c>
       <c r="G120" s="4" t="n">
-        <v>-4647.835084111391</v>
+        <v>-4292.258338493595</v>
       </c>
       <c r="H120" s="4" t="n">
-        <v>7901.800187455695</v>
+        <v>8488.151163055478</v>
       </c>
       <c r="I120" s="3" t="inlineStr"/>
     </row>
@@ -5230,16 +5486,16 @@
         <v>-6</v>
       </c>
       <c r="E121" s="4" t="n">
-        <v>2411.89656559884</v>
+        <v>2457.872098722581</v>
       </c>
       <c r="F121" s="4" t="n">
-        <v>3065.844586437675</v>
+        <v>3195.617638457022</v>
       </c>
       <c r="G121" s="4" t="n">
-        <v>-3597.158823819002</v>
+        <v>-3805.538472653182</v>
       </c>
       <c r="H121" s="4" t="n">
-        <v>8420.951955016684</v>
+        <v>8721.282670098344</v>
       </c>
       <c r="I121" s="3" t="inlineStr"/>
     </row>
@@ -5263,16 +5519,16 @@
         <v>-5</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>2460.049436832921</v>
+        <v>2499.173532475725</v>
       </c>
       <c r="F122" s="4" t="n">
-        <v>1697.6452957494</v>
+        <v>1829.174798931218</v>
       </c>
       <c r="G122" s="4" t="n">
-        <v>-867.3353428359032</v>
+        <v>-1086.009073429462</v>
       </c>
       <c r="H122" s="4" t="n">
-        <v>5787.434216501746</v>
+        <v>6084.356138380912</v>
       </c>
       <c r="I122" s="3" t="inlineStr"/>
     </row>
@@ -5296,16 +5552,16 @@
         <v>-4</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>933.0136974059338</v>
+        <v>969.8662558724669</v>
       </c>
       <c r="F123" s="4" t="n">
-        <v>1274.347975074508</v>
+        <v>1263.691669680675</v>
       </c>
       <c r="G123" s="4" t="n">
-        <v>-1564.708333740102</v>
+        <v>-1506.969416701656</v>
       </c>
       <c r="H123" s="4" t="n">
-        <v>3430.735728551969</v>
+        <v>3446.70192844659</v>
       </c>
       <c r="I123" s="3" t="inlineStr"/>
     </row>
@@ -5329,16 +5585,16 @@
         <v>-3</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>692.0312982746477</v>
+        <v>728.4243409746683</v>
       </c>
       <c r="F124" s="4" t="n">
-        <v>866.6555674414112</v>
+        <v>905.4217157385441</v>
       </c>
       <c r="G124" s="4" t="n">
-        <v>-1006.613613910518</v>
+        <v>-1046.202221872878</v>
       </c>
       <c r="H124" s="4" t="n">
-        <v>2390.676210459814</v>
+        <v>2503.050903822215</v>
       </c>
       <c r="I124" s="3" t="inlineStr"/>
     </row>
@@ -5362,16 +5618,16 @@
         <v>-2</v>
       </c>
       <c r="E125" s="4" t="n">
-        <v>6194.355933812401</v>
+        <v>6225.128435868297</v>
       </c>
       <c r="F125" s="4" t="n">
-        <v>7035.168111942572</v>
+        <v>6718.273236715831</v>
       </c>
       <c r="G125" s="4" t="n">
-        <v>-7594.573565595039</v>
+        <v>-6942.687108094731</v>
       </c>
       <c r="H125" s="4" t="n">
-        <v>19983.28543321984</v>
+        <v>19392.94397983133</v>
       </c>
       <c r="I125" s="3" t="inlineStr"/>
     </row>
@@ -5395,16 +5651,16 @@
         <v>-1</v>
       </c>
       <c r="E126" s="4" t="n">
-        <v>4184.624987641462</v>
+        <v>4218.195538390153</v>
       </c>
       <c r="F126" s="4" t="n">
-        <v>3723.235526674913</v>
+        <v>3699.899330726515</v>
       </c>
       <c r="G126" s="4" t="n">
-        <v>-3112.916644641366</v>
+        <v>-3033.607149833815</v>
       </c>
       <c r="H126" s="4" t="n">
-        <v>11482.16661992429</v>
+        <v>11469.99822661412</v>
       </c>
       <c r="I126" s="3" t="inlineStr"/>
     </row>
@@ -5428,16 +5684,16 @@
         <v>0</v>
       </c>
       <c r="E127" s="4" t="n">
-        <v>-841.9137643998774</v>
+        <v>-844.5554705335802</v>
       </c>
       <c r="F127" s="4" t="n">
-        <v>2165.292857271847</v>
+        <v>2111.75763563955</v>
       </c>
       <c r="G127" s="4" t="n">
-        <v>-5085.887764652696</v>
+        <v>-4983.600436387097</v>
       </c>
       <c r="H127" s="4" t="n">
-        <v>3402.060235852941</v>
+        <v>3294.489495319937</v>
       </c>
       <c r="I127" s="3" t="inlineStr"/>
     </row>
@@ -5461,18 +5717,18 @@
         <v>1</v>
       </c>
       <c r="E128" s="6" t="n">
-        <v>8173.745810438205</v>
+        <v>8162.210238141843</v>
       </c>
       <c r="F128" s="6" t="n">
-        <v>3831.53090223597</v>
+        <v>3709.183071666453</v>
       </c>
       <c r="G128" s="4" t="n">
-        <v>663.9452420557036</v>
+        <v>892.2114176755958</v>
       </c>
       <c r="H128" s="4" t="n">
-        <v>15683.54637882071</v>
-      </c>
-      <c r="I128" s="13" t="inlineStr">
+        <v>15432.20905860809</v>
+      </c>
+      <c r="I128" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5498,18 +5754,18 @@
         <v>2</v>
       </c>
       <c r="E129" s="6" t="n">
-        <v>10223.05392370293</v>
+        <v>10205.46965550663</v>
       </c>
       <c r="F129" s="6" t="n">
-        <v>3866.768376946061</v>
+        <v>3670.535629622472</v>
       </c>
       <c r="G129" s="4" t="n">
-        <v>2644.187904888649</v>
+        <v>3011.219821446582</v>
       </c>
       <c r="H129" s="4" t="n">
-        <v>17801.91994251721</v>
-      </c>
-      <c r="I129" s="13" t="inlineStr">
+        <v>17399.71948956667</v>
+      </c>
+      <c r="I129" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5535,16 +5791,16 @@
         <v>3</v>
       </c>
       <c r="E130" s="4" t="n">
-        <v>14013.24380104882</v>
+        <v>13989.24068233876</v>
       </c>
       <c r="F130" s="4" t="n">
-        <v>9282.202516991592</v>
+        <v>9411.220340068076</v>
       </c>
       <c r="G130" s="4" t="n">
-        <v>-4179.873132254705</v>
+        <v>-4456.751184194663</v>
       </c>
       <c r="H130" s="4" t="n">
-        <v>32206.36073435234</v>
+        <v>32435.23254887219</v>
       </c>
       <c r="I130" s="3" t="inlineStr"/>
     </row>
@@ -5568,16 +5824,16 @@
         <v>4</v>
       </c>
       <c r="E131" s="4" t="n">
-        <v>21268.26972715855</v>
+        <v>21236.8351245929</v>
       </c>
       <c r="F131" s="4" t="n">
-        <v>13119.67920549415</v>
+        <v>11132.41146253121</v>
       </c>
       <c r="G131" s="4" t="n">
-        <v>-4446.301515609986</v>
+        <v>-582.6913419682642</v>
       </c>
       <c r="H131" s="4" t="n">
-        <v>46982.84096992709</v>
+        <v>43056.36159115407</v>
       </c>
       <c r="I131" s="3" t="inlineStr"/>
     </row>
@@ -5601,18 +5857,18 @@
         <v>5</v>
       </c>
       <c r="E132" s="6" t="n">
-        <v>33202.06331295872</v>
+        <v>33161.76449645292</v>
       </c>
       <c r="F132" s="6" t="n">
-        <v>14786.35397409237</v>
+        <v>14398.98503671645</v>
       </c>
       <c r="G132" s="4" t="n">
-        <v>4220.809523737673</v>
+        <v>4939.753824488678</v>
       </c>
       <c r="H132" s="4" t="n">
-        <v>62183.31710217978</v>
-      </c>
-      <c r="I132" s="13" t="inlineStr">
+        <v>61383.77516841717</v>
+      </c>
+      <c r="I132" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5638,18 +5894,18 @@
         <v>6</v>
       </c>
       <c r="E133" s="6" t="n">
-        <v>26310.99173122785</v>
+        <v>26256.93762873745</v>
       </c>
       <c r="F133" s="6" t="n">
-        <v>2468.973372644269</v>
+        <v>2392.294699098601</v>
       </c>
       <c r="G133" s="4" t="n">
-        <v>21471.80392084509</v>
+        <v>21568.04001850419</v>
       </c>
       <c r="H133" s="4" t="n">
-        <v>31150.17954161062</v>
-      </c>
-      <c r="I133" s="13" t="inlineStr">
+        <v>30945.83523897071</v>
+      </c>
+      <c r="I133" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -5675,16 +5931,16 @@
         <v>-7</v>
       </c>
       <c r="E134" s="4" t="n">
-        <v>1287.791666666687</v>
+        <v>3692.029761904759</v>
       </c>
       <c r="F134" s="4" t="n">
-        <v>5652.14824755317</v>
+        <v>5610.460331573942</v>
       </c>
       <c r="G134" s="4" t="n">
-        <v>-9790.418898537528</v>
+        <v>-7304.472487980167</v>
       </c>
       <c r="H134" s="4" t="n">
-        <v>12366.0022318709</v>
+        <v>14688.53201178969</v>
       </c>
       <c r="I134" s="3" t="inlineStr"/>
     </row>
@@ -5708,16 +5964,16 @@
         <v>-6</v>
       </c>
       <c r="E135" s="4" t="n">
-        <v>4355.837784656562</v>
+        <v>4653.360835873988</v>
       </c>
       <c r="F135" s="4" t="n">
-        <v>6811.898437821154</v>
+        <v>7088.201925500872</v>
       </c>
       <c r="G135" s="4" t="n">
-        <v>-8995.4831534729</v>
+        <v>-9239.514938107721</v>
       </c>
       <c r="H135" s="4" t="n">
-        <v>17707.15872278602</v>
+        <v>18546.2366098557</v>
       </c>
       <c r="I135" s="3" t="inlineStr"/>
     </row>
@@ -5741,16 +5997,16 @@
         <v>-5</v>
       </c>
       <c r="E136" s="4" t="n">
-        <v>2894.323984265709</v>
+        <v>3207.318304275025</v>
       </c>
       <c r="F136" s="4" t="n">
-        <v>3303.197844768496</v>
+        <v>3579.198691260773</v>
       </c>
       <c r="G136" s="4" t="n">
-        <v>-3579.943791480543</v>
+        <v>-3807.911130596089</v>
       </c>
       <c r="H136" s="4" t="n">
-        <v>9368.591760011961</v>
+        <v>10222.54773914614</v>
       </c>
       <c r="I136" s="3" t="inlineStr"/>
     </row>
@@ -5774,16 +6030,16 @@
         <v>-4</v>
       </c>
       <c r="E137" s="4" t="n">
-        <v>-1047.184141411343</v>
+        <v>-811.9494234994295</v>
       </c>
       <c r="F137" s="4" t="n">
-        <v>2788.360741150482</v>
+        <v>2849.783233640022</v>
       </c>
       <c r="G137" s="4" t="n">
-        <v>-6512.371194066288</v>
+        <v>-6397.524561433873</v>
       </c>
       <c r="H137" s="4" t="n">
-        <v>4418.002911243601</v>
+        <v>4773.625714435013</v>
       </c>
       <c r="I137" s="3" t="inlineStr"/>
     </row>
@@ -5807,16 +6063,16 @@
         <v>-3</v>
       </c>
       <c r="E138" s="4" t="n">
-        <v>1889.645519006151</v>
+        <v>2104.502473506303</v>
       </c>
       <c r="F138" s="4" t="n">
-        <v>1691.728166600908</v>
+        <v>1840.272632585102</v>
       </c>
       <c r="G138" s="4" t="n">
-        <v>-1426.141687531628</v>
+        <v>-1502.431886360496</v>
       </c>
       <c r="H138" s="4" t="n">
-        <v>5205.432725543931</v>
+        <v>5711.436833373102</v>
       </c>
       <c r="I138" s="3" t="inlineStr"/>
     </row>
@@ -5840,16 +6096,16 @@
         <v>-2</v>
       </c>
       <c r="E139" s="4" t="n">
-        <v>4359.103712153576</v>
+        <v>4558.468410966673</v>
       </c>
       <c r="F139" s="4" t="n">
-        <v>2369.932788714926</v>
+        <v>2391.900663791312</v>
       </c>
       <c r="G139" s="4" t="n">
-        <v>-285.9645537276783</v>
+        <v>-129.6568900642988</v>
       </c>
       <c r="H139" s="4" t="n">
-        <v>9004.171978034832</v>
+        <v>9246.593711997644</v>
       </c>
       <c r="I139" s="3" t="inlineStr"/>
     </row>
@@ -5873,16 +6129,16 @@
         <v>-1</v>
       </c>
       <c r="E140" s="4" t="n">
-        <v>1963.661392826118</v>
+        <v>2169.35296582534</v>
       </c>
       <c r="F140" s="4" t="n">
-        <v>2461.679833432853</v>
+        <v>2276.53066783427</v>
       </c>
       <c r="G140" s="4" t="n">
-        <v>-2861.231080702275</v>
+        <v>-2292.647143129829</v>
       </c>
       <c r="H140" s="4" t="n">
-        <v>6788.55386635451</v>
+        <v>6631.353074780509</v>
       </c>
       <c r="I140" s="3" t="inlineStr"/>
     </row>
@@ -5906,16 +6162,16 @@
         <v>0</v>
       </c>
       <c r="E141" s="4" t="n">
-        <v>1956.554630291669</v>
+        <v>1976.703838398222</v>
       </c>
       <c r="F141" s="4" t="n">
-        <v>3174.088777985412</v>
+        <v>3096.111673836473</v>
       </c>
       <c r="G141" s="4" t="n">
-        <v>-4264.659374559737</v>
+        <v>-4091.675042321264</v>
       </c>
       <c r="H141" s="4" t="n">
-        <v>8177.768635143076</v>
+        <v>8045.082719117709</v>
       </c>
       <c r="I141" s="3" t="inlineStr"/>
     </row>
@@ -5939,16 +6195,16 @@
         <v>1</v>
       </c>
       <c r="E142" s="4" t="n">
-        <v>2392.247858053448</v>
+        <v>2421.844628397074</v>
       </c>
       <c r="F142" s="4" t="n">
-        <v>1944.338915378833</v>
+        <v>1862.068879551937</v>
       </c>
       <c r="G142" s="4" t="n">
-        <v>-1418.656416089064</v>
+        <v>-1227.810375524721</v>
       </c>
       <c r="H142" s="4" t="n">
-        <v>6203.15213219596</v>
+        <v>6071.49963231887</v>
       </c>
       <c r="I142" s="3" t="inlineStr"/>
     </row>
@@ -5972,16 +6228,16 @@
         <v>2</v>
       </c>
       <c r="E143" s="4" t="n">
-        <v>3543.522425230933</v>
+        <v>3580.365780880451</v>
       </c>
       <c r="F143" s="4" t="n">
-        <v>3053.700498589431</v>
+        <v>3167.889657492892</v>
       </c>
       <c r="G143" s="4" t="n">
-        <v>-2441.730552004352</v>
+        <v>-2628.697947805617</v>
       </c>
       <c r="H143" s="4" t="n">
-        <v>9528.775402466219</v>
+        <v>9789.42950956652</v>
       </c>
       <c r="I143" s="3" t="inlineStr"/>
     </row>
@@ -6005,16 +6261,16 @@
         <v>3</v>
       </c>
       <c r="E144" s="4" t="n">
-        <v>11460.0718169024</v>
+        <v>11502.33254555521</v>
       </c>
       <c r="F144" s="4" t="n">
-        <v>7548.803842046535</v>
+        <v>7522.893765997339</v>
       </c>
       <c r="G144" s="4" t="n">
-        <v>-3335.583713508811</v>
+        <v>-3242.53923579957</v>
       </c>
       <c r="H144" s="4" t="n">
-        <v>26255.7273473136</v>
+        <v>26247.20432691</v>
       </c>
       <c r="I144" s="3" t="inlineStr"/>
     </row>
@@ -6038,16 +6294,16 @@
         <v>4</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>21057.80960462877</v>
+        <v>21118.49922956029</v>
       </c>
       <c r="F145" s="4" t="n">
-        <v>21217.41698605779</v>
+        <v>20764.80992314647</v>
       </c>
       <c r="G145" s="4" t="n">
-        <v>-20528.3276880445</v>
+        <v>-19580.52821980679</v>
       </c>
       <c r="H145" s="4" t="n">
-        <v>62643.94689730204</v>
+        <v>61817.52667892738</v>
       </c>
       <c r="I145" s="3" t="inlineStr"/>
     </row>
@@ -6071,16 +6327,16 @@
         <v>5</v>
       </c>
       <c r="E146" s="4" t="n">
-        <v>50602.69339008867</v>
+        <v>50701.18953026951</v>
       </c>
       <c r="F146" s="4" t="n">
-        <v>36258.68085004758</v>
+        <v>59722.37207442278</v>
       </c>
       <c r="G146" s="4" t="n">
-        <v>-20464.32107600459</v>
+        <v>-66354.65973559915</v>
       </c>
       <c r="H146" s="4" t="n">
-        <v>121669.7078561819</v>
+        <v>167757.0387961382</v>
       </c>
       <c r="I146" s="3" t="inlineStr"/>
     </row>
@@ -6104,16 +6360,16 @@
         <v>6</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>7417.039880952367</v>
+        <v>7530.70138888889</v>
       </c>
       <c r="F147" s="4" t="n">
-        <v>6288.906790827163</v>
+        <v>6197.353650574192</v>
       </c>
       <c r="G147" s="4" t="n">
-        <v>-4909.217429068873</v>
+        <v>-4616.111766236528</v>
       </c>
       <c r="H147" s="4" t="n">
-        <v>19743.29719097361</v>
+        <v>19677.51454401431</v>
       </c>
       <c r="I147" s="3" t="inlineStr"/>
     </row>
@@ -6137,16 +6393,16 @@
         <v>-7</v>
       </c>
       <c r="E148" s="4" t="n">
-        <v>271.0973145071994</v>
+        <v>540.3095238095257</v>
       </c>
       <c r="F148" s="4" t="n">
-        <v>781.3841103623566</v>
+        <v>761.1292329704193</v>
       </c>
       <c r="G148" s="4" t="n">
-        <v>-1260.41554180302</v>
+        <v>-951.503772812496</v>
       </c>
       <c r="H148" s="4" t="n">
-        <v>1802.610170817418</v>
+        <v>2032.122820431547</v>
       </c>
       <c r="I148" s="3" t="inlineStr"/>
     </row>
@@ -6170,16 +6426,16 @@
         <v>-6</v>
       </c>
       <c r="E149" s="4" t="n">
-        <v>671.3988406338153</v>
+        <v>703.121046112807</v>
       </c>
       <c r="F149" s="4" t="n">
-        <v>719.0774751914863</v>
+        <v>720.6309618638907</v>
       </c>
       <c r="G149" s="4" t="n">
-        <v>-737.9930107414978</v>
+        <v>-709.3156391404187</v>
       </c>
       <c r="H149" s="4" t="n">
-        <v>2080.790692009128</v>
+        <v>2115.557731366033</v>
       </c>
       <c r="I149" s="3" t="inlineStr"/>
     </row>
@@ -6203,16 +6459,16 @@
         <v>-5</v>
       </c>
       <c r="E150" s="4" t="n">
-        <v>348.9253855176797</v>
+        <v>376.8848601260859</v>
       </c>
       <c r="F150" s="4" t="n">
-        <v>328.9378775872837</v>
+        <v>330.4097386148474</v>
       </c>
       <c r="G150" s="4" t="n">
-        <v>-295.7928545533963</v>
+        <v>-270.718227559015</v>
       </c>
       <c r="H150" s="4" t="n">
-        <v>993.6436255887558</v>
+        <v>1024.487947811187</v>
       </c>
       <c r="I150" s="3" t="inlineStr"/>
     </row>
@@ -6236,16 +6492,16 @@
         <v>-4</v>
       </c>
       <c r="E151" s="4" t="n">
-        <v>-94.10017953398386</v>
+        <v>-70.66634641327923</v>
       </c>
       <c r="F151" s="4" t="n">
-        <v>449.6806095589185</v>
+        <v>425.2759092902124</v>
       </c>
       <c r="G151" s="4" t="n">
-        <v>-975.4741742694641</v>
+        <v>-904.2071286220956</v>
       </c>
       <c r="H151" s="4" t="n">
-        <v>787.2738152014963</v>
+        <v>762.8744357955371</v>
       </c>
       <c r="I151" s="3" t="inlineStr"/>
     </row>
@@ -6269,16 +6525,16 @@
         <v>-3</v>
       </c>
       <c r="E152" s="4" t="n">
-        <v>119.2646745966656</v>
+        <v>128.2083487511565</v>
       </c>
       <c r="F152" s="4" t="n">
-        <v>219.8993781187881</v>
+        <v>235.6713995599049</v>
       </c>
       <c r="G152" s="4" t="n">
-        <v>-311.738106516159</v>
+        <v>-333.7075943862571</v>
       </c>
       <c r="H152" s="4" t="n">
-        <v>550.2674557094903</v>
+        <v>590.1242918885702</v>
       </c>
       <c r="I152" s="3" t="inlineStr"/>
     </row>
@@ -6302,16 +6558,16 @@
         <v>-2</v>
       </c>
       <c r="E153" s="4" t="n">
-        <v>765.2423271806319</v>
+        <v>781.7539475420282</v>
       </c>
       <c r="F153" s="4" t="n">
-        <v>515.0051650111477</v>
+        <v>514.5629918489003</v>
       </c>
       <c r="G153" s="4" t="n">
-        <v>-244.1677962412175</v>
+        <v>-226.7895164818163</v>
       </c>
       <c r="H153" s="4" t="n">
-        <v>1774.652450602481</v>
+        <v>1790.297411565873</v>
       </c>
       <c r="I153" s="3" t="inlineStr"/>
     </row>
@@ -6335,16 +6591,16 @@
         <v>-1</v>
       </c>
       <c r="E154" s="4" t="n">
-        <v>45.79802697663581</v>
+        <v>69.60659259060193</v>
       </c>
       <c r="F154" s="4" t="n">
-        <v>392.8729484754252</v>
+        <v>415.9435023884816</v>
       </c>
       <c r="G154" s="4" t="n">
-        <v>-724.2329520351975</v>
+        <v>-745.6426720908221</v>
       </c>
       <c r="H154" s="4" t="n">
-        <v>815.8290059884691</v>
+        <v>884.855857272026</v>
       </c>
       <c r="I154" s="3" t="inlineStr"/>
     </row>
@@ -6368,16 +6624,16 @@
         <v>0</v>
       </c>
       <c r="E155" s="4" t="n">
-        <v>22.25019095833002</v>
+        <v>30.78165803029079</v>
       </c>
       <c r="F155" s="4" t="n">
-        <v>323.0310592327976</v>
+        <v>312.5689088021347</v>
       </c>
       <c r="G155" s="4" t="n">
-        <v>-610.8906851379533</v>
+        <v>-581.8534032218931</v>
       </c>
       <c r="H155" s="4" t="n">
-        <v>655.3910670546132</v>
+        <v>643.4167192824748</v>
       </c>
       <c r="I155" s="3" t="inlineStr"/>
     </row>
@@ -6401,16 +6657,16 @@
         <v>1</v>
       </c>
       <c r="E156" s="4" t="n">
-        <v>-1173.880788578548</v>
+        <v>-1175.27808595632</v>
       </c>
       <c r="F156" s="4" t="n">
-        <v>1881.79676615732</v>
+        <v>1861.93704321402</v>
       </c>
       <c r="G156" s="4" t="n">
-        <v>-4862.202450246894</v>
+        <v>-4824.674690655798</v>
       </c>
       <c r="H156" s="4" t="n">
-        <v>2514.440873089798</v>
+        <v>2474.118518743159</v>
       </c>
       <c r="I156" s="3" t="inlineStr"/>
     </row>
@@ -6434,16 +6690,16 @@
         <v>2</v>
       </c>
       <c r="E157" s="4" t="n">
-        <v>-1627.509882364014</v>
+        <v>-1633.62248542773</v>
       </c>
       <c r="F157" s="4" t="n">
-        <v>3362.542199862911</v>
+        <v>3450.183122888918</v>
       </c>
       <c r="G157" s="4" t="n">
-        <v>-8218.092594095318</v>
+        <v>-8395.98140629001</v>
       </c>
       <c r="H157" s="4" t="n">
-        <v>4963.072829367291</v>
+        <v>5128.736435434549</v>
       </c>
       <c r="I157" s="3" t="inlineStr"/>
     </row>
@@ -6467,16 +6723,16 @@
         <v>3</v>
       </c>
       <c r="E158" s="4" t="n">
-        <v>-894.5610101219845</v>
+        <v>-908.2783776301214</v>
       </c>
       <c r="F158" s="4" t="n">
-        <v>2303.907538399625</v>
+        <v>2263.202734634667</v>
       </c>
       <c r="G158" s="4" t="n">
-        <v>-5410.219785385249</v>
+        <v>-5344.155737514068</v>
       </c>
       <c r="H158" s="4" t="n">
-        <v>3621.09776514128</v>
+        <v>3527.598982253826</v>
       </c>
       <c r="I158" s="3" t="inlineStr"/>
     </row>
@@ -6500,16 +6756,16 @@
         <v>4</v>
       </c>
       <c r="E159" s="4" t="n">
-        <v>1584.179183865232</v>
+        <v>1572.096832527938</v>
       </c>
       <c r="F159" s="4" t="n">
-        <v>1116.897824523305</v>
+        <v>1138.083040451413</v>
       </c>
       <c r="G159" s="4" t="n">
-        <v>-604.9405522004458</v>
+        <v>-658.5459267568312</v>
       </c>
       <c r="H159" s="4" t="n">
-        <v>3773.298919930909</v>
+        <v>3802.739591812708</v>
       </c>
       <c r="I159" s="3" t="inlineStr"/>
     </row>
@@ -6532,23 +6788,19 @@
       <c r="D160" s="3" t="n">
         <v>5</v>
       </c>
-      <c r="E160" s="6" t="n">
-        <v>6706.247289128827</v>
-      </c>
-      <c r="F160" s="6" t="n">
-        <v>3253.971093367236</v>
+      <c r="E160" s="4" t="n">
+        <v>6699.053047711333</v>
+      </c>
+      <c r="F160" s="4" t="n">
+        <v>4993.927127790392</v>
       </c>
       <c r="G160" s="4" t="n">
-        <v>328.4639461290453</v>
+        <v>-3089.044122757835</v>
       </c>
       <c r="H160" s="4" t="n">
-        <v>13084.03063212861</v>
-      </c>
-      <c r="I160" s="13" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+        <v>16487.1502181805</v>
+      </c>
+      <c r="I160" s="3" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="3" t="inlineStr">
@@ -6570,18 +6822,18 @@
         <v>6</v>
       </c>
       <c r="E161" s="6" t="n">
-        <v>3675.567460317461</v>
+        <v>3675.091468253968</v>
       </c>
       <c r="F161" s="6" t="n">
-        <v>572.5540675005642</v>
+        <v>581.7101286636251</v>
       </c>
       <c r="G161" s="4" t="n">
-        <v>2553.361488016355</v>
+        <v>2534.939616073263</v>
       </c>
       <c r="H161" s="4" t="n">
-        <v>4797.773432618566</v>
-      </c>
-      <c r="I161" s="13" t="inlineStr">
+        <v>4815.243320434673</v>
+      </c>
+      <c r="I161" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -6607,16 +6859,16 @@
         <v>-7</v>
       </c>
       <c r="E162" s="4" t="n">
-        <v>145.4403377630092</v>
+        <v>907.690476190466</v>
       </c>
       <c r="F162" s="4" t="n">
-        <v>1569.048964031579</v>
+        <v>1651.32050192116</v>
       </c>
       <c r="G162" s="4" t="n">
-        <v>-2929.895631738885</v>
+        <v>-2328.897707575009</v>
       </c>
       <c r="H162" s="4" t="n">
-        <v>3220.776307264903</v>
+        <v>4144.27865995594</v>
       </c>
       <c r="I162" s="3" t="inlineStr"/>
     </row>
@@ -6640,16 +6892,16 @@
         <v>-6</v>
       </c>
       <c r="E163" s="4" t="n">
-        <v>451.8316132093131</v>
+        <v>547.3708714430857</v>
       </c>
       <c r="F163" s="4" t="n">
-        <v>1503.020683010926</v>
+        <v>1577.40346267907</v>
       </c>
       <c r="G163" s="4" t="n">
-        <v>-2494.088925492101</v>
+        <v>-2544.339915407891</v>
       </c>
       <c r="H163" s="4" t="n">
-        <v>3397.752151910728</v>
+        <v>3639.081658294062</v>
       </c>
       <c r="I163" s="3" t="inlineStr"/>
     </row>
@@ -6673,16 +6925,16 @@
         <v>-5</v>
       </c>
       <c r="E164" s="4" t="n">
-        <v>1384.13410316255</v>
+        <v>1459.531523345147</v>
       </c>
       <c r="F164" s="4" t="n">
-        <v>2298.045580256554</v>
+        <v>2363.501985746265</v>
       </c>
       <c r="G164" s="4" t="n">
-        <v>-3120.035234140296</v>
+        <v>-3172.932368717533</v>
       </c>
       <c r="H164" s="4" t="n">
-        <v>5888.303440465395</v>
+        <v>6091.995415407826</v>
       </c>
       <c r="I164" s="3" t="inlineStr"/>
     </row>
@@ -6706,16 +6958,16 @@
         <v>-4</v>
       </c>
       <c r="E165" s="4" t="n">
-        <v>-259.1335108009266</v>
+        <v>-216.7152992614168</v>
       </c>
       <c r="F165" s="4" t="n">
-        <v>397.9720524083674</v>
+        <v>410.0668476272075</v>
       </c>
       <c r="G165" s="4" t="n">
-        <v>-1039.158733521327</v>
+        <v>-1020.446320610743</v>
       </c>
       <c r="H165" s="4" t="n">
-        <v>520.8917119194734</v>
+        <v>587.0157220879098</v>
       </c>
       <c r="I165" s="3" t="inlineStr"/>
     </row>
@@ -6739,16 +6991,16 @@
         <v>-3</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>-360.7497392818876</v>
+        <v>-287.8667500338757</v>
       </c>
       <c r="F166" s="4" t="n">
-        <v>412.1893692734964</v>
+        <v>389.1996505558822</v>
       </c>
       <c r="G166" s="4" t="n">
-        <v>-1168.64090305794</v>
+        <v>-1050.698065123405</v>
       </c>
       <c r="H166" s="4" t="n">
-        <v>447.1414244941654</v>
+        <v>474.9645650556533</v>
       </c>
       <c r="I166" s="3" t="inlineStr"/>
     </row>
@@ -6772,16 +7024,16 @@
         <v>-2</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>1262.755032966795</v>
+        <v>1338.848304566973</v>
       </c>
       <c r="F167" s="4" t="n">
-        <v>1011.00790870815</v>
+        <v>1152.054760585987</v>
       </c>
       <c r="G167" s="4" t="n">
-        <v>-718.820468101178</v>
+        <v>-919.1790261815624</v>
       </c>
       <c r="H167" s="4" t="n">
-        <v>3244.330534034769</v>
+        <v>3596.875635315509</v>
       </c>
       <c r="I167" s="3" t="inlineStr"/>
     </row>
@@ -6805,16 +7057,16 @@
         <v>-1</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>-601.7797564489787</v>
+        <v>-524.0948133577783</v>
       </c>
       <c r="F168" s="4" t="n">
-        <v>1751.867617587054</v>
+        <v>1589.431763651564</v>
       </c>
       <c r="G168" s="4" t="n">
-        <v>-4035.440286919605</v>
+        <v>-3639.381070114844</v>
       </c>
       <c r="H168" s="4" t="n">
-        <v>2831.880774021648</v>
+        <v>2591.191443399288</v>
       </c>
       <c r="I168" s="3" t="inlineStr"/>
     </row>
@@ -6838,16 +7090,16 @@
         <v>0</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>269.8119658075098</v>
+        <v>280.4964462908026</v>
       </c>
       <c r="F169" s="4" t="n">
-        <v>1280.371058597899</v>
+        <v>1347.882136817284</v>
       </c>
       <c r="G169" s="4" t="n">
-        <v>-2239.715309044373</v>
+        <v>-2361.352541871075</v>
       </c>
       <c r="H169" s="4" t="n">
-        <v>2779.339240659393</v>
+        <v>2922.34543445268</v>
       </c>
       <c r="I169" s="3" t="inlineStr"/>
     </row>
@@ -6871,16 +7123,16 @@
         <v>1</v>
       </c>
       <c r="E170" s="4" t="n">
-        <v>4490.68775037884</v>
+        <v>4501.356514212019</v>
       </c>
       <c r="F170" s="4" t="n">
-        <v>3246.737304224729</v>
+        <v>3259.361846365852</v>
       </c>
       <c r="G170" s="4" t="n">
-        <v>-1872.917365901629</v>
+        <v>-1886.992704665051</v>
       </c>
       <c r="H170" s="4" t="n">
-        <v>10854.29286665931</v>
+        <v>10889.70573308909</v>
       </c>
       <c r="I170" s="3" t="inlineStr"/>
     </row>
@@ -6904,16 +7156,16 @@
         <v>2</v>
       </c>
       <c r="E171" s="4" t="n">
-        <v>9801.86627367857</v>
+        <v>9814.554414209275</v>
       </c>
       <c r="F171" s="4" t="n">
-        <v>8879.393167866912</v>
+        <v>8445.020821801634</v>
       </c>
       <c r="G171" s="4" t="n">
-        <v>-7601.744335340576</v>
+        <v>-6737.686396521929</v>
       </c>
       <c r="H171" s="4" t="n">
-        <v>27205.47688269772</v>
+        <v>26366.79522494048</v>
       </c>
       <c r="I171" s="3" t="inlineStr"/>
     </row>
@@ -6937,16 +7189,16 @@
         <v>3</v>
       </c>
       <c r="E172" s="4" t="n">
-        <v>20996.14709700829</v>
+        <v>21013.65917123897</v>
       </c>
       <c r="F172" s="4" t="n">
-        <v>19868.85480995001</v>
+        <v>21488.51322988882</v>
       </c>
       <c r="G172" s="4" t="n">
-        <v>-17946.80833049372</v>
+        <v>-21103.82675934312</v>
       </c>
       <c r="H172" s="4" t="n">
-        <v>59939.1025245103</v>
+        <v>63131.14510182106</v>
       </c>
       <c r="I172" s="3" t="inlineStr"/>
     </row>
@@ -6970,16 +7222,16 @@
         <v>4</v>
       </c>
       <c r="E173" s="4" t="n">
-        <v>31406.64334960905</v>
+        <v>31423.66700378648</v>
       </c>
       <c r="F173" s="4" t="n">
-        <v>27793.35649778342</v>
+        <v>25482.88799263597</v>
       </c>
       <c r="G173" s="4" t="n">
-        <v>-23068.33538604646</v>
+        <v>-18522.79346178003</v>
       </c>
       <c r="H173" s="4" t="n">
-        <v>85881.62208526456</v>
+        <v>81370.12746935298</v>
       </c>
       <c r="I173" s="3" t="inlineStr"/>
     </row>
@@ -7003,16 +7255,16 @@
         <v>5</v>
       </c>
       <c r="E174" s="4" t="n">
-        <v>50438.39242340347</v>
+        <v>50464.64786590993</v>
       </c>
       <c r="F174" s="4" t="n">
-        <v>58979.45423780426</v>
+        <v>58621.06868846739</v>
       </c>
       <c r="G174" s="4" t="n">
-        <v>-65161.33788269287</v>
+        <v>-64432.64676348614</v>
       </c>
       <c r="H174" s="4" t="n">
-        <v>166038.1227294998</v>
+        <v>165361.942495306</v>
       </c>
       <c r="I174" s="3" t="inlineStr"/>
     </row>
@@ -7036,18 +7288,18 @@
         <v>6</v>
       </c>
       <c r="E175" s="6" t="n">
-        <v>7650.669444444444</v>
+        <v>7683.16111111111</v>
       </c>
       <c r="F175" s="6" t="n">
-        <v>1966.932716775079</v>
+        <v>2116.771628895333</v>
       </c>
       <c r="G175" s="4" t="n">
-        <v>3795.481319565289</v>
+        <v>3534.288718476257</v>
       </c>
       <c r="H175" s="4" t="n">
-        <v>11505.8575693236</v>
-      </c>
-      <c r="I175" s="13" t="inlineStr">
+        <v>11832.03350374596</v>
+      </c>
+      <c r="I175" s="14" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
@@ -7075,22 +7327,22 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="14" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Threshold</t>
         </is>
       </c>
-      <c r="B1" s="14" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>Cohort Year</t>
         </is>
       </c>
-      <c r="C1" s="14" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t># States</t>
         </is>
       </c>
-      <c r="D1" s="14" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>States</t>
         </is>
@@ -7404,82 +7656,82 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="15" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="B2" s="15" t="inlineStr">
+      <c r="B2" s="16" t="inlineStr">
         <is>
           <t>ATT</t>
         </is>
       </c>
-      <c r="C2" s="15" t="inlineStr">
+      <c r="C2" s="16" t="inlineStr">
         <is>
           <t>CI_lo</t>
         </is>
       </c>
-      <c r="D2" s="15" t="inlineStr">
+      <c r="D2" s="16" t="inlineStr">
         <is>
           <t>CI_hi</t>
         </is>
       </c>
-      <c r="F2" s="15" t="inlineStr">
+      <c r="F2" s="16" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="G2" s="15" t="inlineStr">
+      <c r="G2" s="16" t="inlineStr">
         <is>
           <t>ATT</t>
         </is>
       </c>
-      <c r="H2" s="15" t="inlineStr">
+      <c r="H2" s="16" t="inlineStr">
         <is>
           <t>CI_lo</t>
         </is>
       </c>
-      <c r="I2" s="15" t="inlineStr">
+      <c r="I2" s="16" t="inlineStr">
         <is>
           <t>CI_hi</t>
         </is>
       </c>
-      <c r="K2" s="15" t="inlineStr">
+      <c r="K2" s="16" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="L2" s="15" t="inlineStr">
+      <c r="L2" s="16" t="inlineStr">
         <is>
           <t>ATT</t>
         </is>
       </c>
-      <c r="M2" s="15" t="inlineStr">
+      <c r="M2" s="16" t="inlineStr">
         <is>
           <t>CI_lo</t>
         </is>
       </c>
-      <c r="N2" s="15" t="inlineStr">
+      <c r="N2" s="16" t="inlineStr">
         <is>
           <t>CI_hi</t>
         </is>
       </c>
-      <c r="P2" s="15" t="inlineStr">
+      <c r="P2" s="16" t="inlineStr">
         <is>
           <t>e</t>
         </is>
       </c>
-      <c r="Q2" s="15" t="inlineStr">
+      <c r="Q2" s="16" t="inlineStr">
         <is>
           <t>ATT</t>
         </is>
       </c>
-      <c r="R2" s="15" t="inlineStr">
+      <c r="R2" s="16" t="inlineStr">
         <is>
           <t>CI_lo</t>
         </is>
       </c>
-      <c r="S2" s="15" t="inlineStr">
+      <c r="S2" s="16" t="inlineStr">
         <is>
           <t>CI_hi</t>
         </is>
@@ -7490,49 +7742,49 @@
         <v>-7</v>
       </c>
       <c r="B3" s="4" t="n">
-        <v>-306.3645610297684</v>
+        <v>-216.8931769233062</v>
       </c>
       <c r="C3" s="4" t="n">
-        <v>-594.0033923224545</v>
+        <v>-410.7971160211331</v>
       </c>
       <c r="D3" s="4" t="n">
-        <v>-18.72572973708225</v>
+        <v>-22.98923782547931</v>
       </c>
       <c r="F3" s="3" t="n">
         <v>-7</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>-147.347960992908</v>
+        <v>121.4893617021277</v>
       </c>
       <c r="H3" s="4" t="n">
-        <v>-932.5512920666082</v>
+        <v>-272.663330806267</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>637.8553700807921</v>
+        <v>515.6420542105225</v>
       </c>
       <c r="K3" s="3" t="n">
         <v>-7</v>
       </c>
       <c r="L3" s="4" t="n">
-        <v>285.6537501032847</v>
+        <v>373.0023033502937</v>
       </c>
       <c r="M3" s="4" t="n">
-        <v>-798.0162566023591</v>
+        <v>-761.4166559334572</v>
       </c>
       <c r="N3" s="4" t="n">
-        <v>1369.323756808928</v>
+        <v>1507.421262634045</v>
       </c>
       <c r="P3" s="3" t="n">
         <v>-7</v>
       </c>
       <c r="Q3" s="4" t="n">
-        <v>271.0973145071994</v>
+        <v>540.3095238095257</v>
       </c>
       <c r="R3" s="4" t="n">
-        <v>-1260.41554180302</v>
+        <v>-951.503772812496</v>
       </c>
       <c r="S3" s="4" t="n">
-        <v>1802.610170817418</v>
+        <v>2032.122820431547</v>
       </c>
     </row>
     <row r="4">
@@ -7540,49 +7792,49 @@
         <v>-6</v>
       </c>
       <c r="B4" s="4" t="n">
-        <v>-198.5088552792922</v>
+        <v>-157.1979616228538</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>-429.1180711112</v>
+        <v>-381.1170539916548</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>32.10036055261574</v>
+        <v>66.72113074594714</v>
       </c>
       <c r="F4" s="3" t="n">
         <v>-6</v>
       </c>
       <c r="G4" s="4" t="n">
-        <v>-415.7134404872031</v>
+        <v>-287.1504972247907</v>
       </c>
       <c r="H4" s="4" t="n">
-        <v>-1295.027711204481</v>
+        <v>-1247.790351636229</v>
       </c>
       <c r="I4" s="4" t="n">
-        <v>463.6008302300745</v>
+        <v>673.4893571866478</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>-6</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>431.6477286106806</v>
+        <v>438.4862630832869</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>-654.1394000790131</v>
+        <v>-665.5626286790142</v>
       </c>
       <c r="N4" s="4" t="n">
-        <v>1517.434857300374</v>
+        <v>1542.535154845588</v>
       </c>
       <c r="P4" s="3" t="n">
         <v>-6</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>671.3988406338153</v>
+        <v>703.121046112807</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>-737.9930107414978</v>
+        <v>-709.3156391404187</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>2080.790692009128</v>
+        <v>2115.557731366033</v>
       </c>
     </row>
     <row r="5">
@@ -7590,49 +7842,49 @@
         <v>-5</v>
       </c>
       <c r="B5" s="4" t="n">
-        <v>168.0627432425046</v>
+        <v>221.03265616011</v>
       </c>
       <c r="C5" s="4" t="n">
-        <v>-499.496028121888</v>
+        <v>-470.8536811921084</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>835.6215146068973</v>
+        <v>912.9189935123285</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>265.0217239635992</v>
+        <v>433.2332844624203</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-677.1113320694317</v>
+        <v>-514.0316129155185</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>1207.15477999663</v>
+        <v>1380.498181840359</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>420.775428248567</v>
+        <v>426.792054017921</v>
       </c>
       <c r="M5" s="4" t="n">
-        <v>-143.1287072556232</v>
+        <v>-207.6550474001042</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>984.6795637527573</v>
+        <v>1061.239155435946</v>
       </c>
       <c r="P5" s="3" t="n">
         <v>-5</v>
       </c>
       <c r="Q5" s="4" t="n">
-        <v>348.9253855176797</v>
+        <v>376.8848601260859</v>
       </c>
       <c r="R5" s="4" t="n">
-        <v>-295.7928545533963</v>
+        <v>-270.718227559015</v>
       </c>
       <c r="S5" s="4" t="n">
-        <v>993.6436255887558</v>
+        <v>1024.487947811187</v>
       </c>
     </row>
     <row r="6">
@@ -7640,49 +7892,49 @@
         <v>-4</v>
       </c>
       <c r="B6" s="4" t="n">
-        <v>209.1753319635837</v>
+        <v>248.4486700857233</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>-517.78404513796</v>
+        <v>-486.2185732868124</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>936.1347090651275</v>
+        <v>983.115913458259</v>
       </c>
       <c r="F6" s="3" t="n">
         <v>-4</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>397.0246538054978</v>
+        <v>529.8593115750538</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>-532.3702177568684</v>
+        <v>-405.6333543743522</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>1326.419525367864</v>
+        <v>1465.35197752446</v>
       </c>
       <c r="K6" s="3" t="n">
         <v>-4</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>146.0709047003967</v>
+        <v>151.5867039355543</v>
       </c>
       <c r="M6" s="4" t="n">
-        <v>-317.3032486573734</v>
+        <v>-293.8102469668055</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>609.4450580581669</v>
+        <v>596.9836548379141</v>
       </c>
       <c r="P6" s="3" t="n">
         <v>-4</v>
       </c>
       <c r="Q6" s="4" t="n">
-        <v>-94.10017953398386</v>
+        <v>-70.66634641327923</v>
       </c>
       <c r="R6" s="4" t="n">
-        <v>-975.4741742694641</v>
+        <v>-904.2071286220956</v>
       </c>
       <c r="S6" s="4" t="n">
-        <v>787.2738152014963</v>
+        <v>762.8744357955371</v>
       </c>
     </row>
     <row r="7">
@@ -7690,49 +7942,49 @@
         <v>-3</v>
       </c>
       <c r="B7" s="4" t="n">
-        <v>287.6566781481663</v>
+        <v>306.1334533265837</v>
       </c>
       <c r="C7" s="4" t="n">
-        <v>-312.6590436051642</v>
+        <v>-292.2596814922093</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>887.9723999014968</v>
+        <v>904.5265881453766</v>
       </c>
       <c r="F7" s="3" t="n">
         <v>-3</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>95.92410403532442</v>
+        <v>157.1870756276251</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>-788.3428224021477</v>
+        <v>-699.3646887053617</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>980.1910304727965</v>
+        <v>1013.738839960612</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>-3</v>
       </c>
       <c r="L7" s="4" t="n">
-        <v>110.8433519167631</v>
+        <v>116.4239305450163</v>
       </c>
       <c r="M7" s="4" t="n">
-        <v>-243.8113187098147</v>
+        <v>-227.4495835788991</v>
       </c>
       <c r="N7" s="4" t="n">
-        <v>465.4980225433408</v>
+        <v>460.2974446689317</v>
       </c>
       <c r="P7" s="3" t="n">
         <v>-3</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>119.2646745966656</v>
+        <v>128.2083487511565</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>-311.738106516159</v>
+        <v>-333.7075943862571</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>550.2674557094903</v>
+        <v>590.1242918885702</v>
       </c>
     </row>
     <row r="8">
@@ -7740,49 +7992,49 @@
         <v>-2</v>
       </c>
       <c r="B8" s="4" t="n">
-        <v>237.6835484940758</v>
+        <v>249.7386694892955</v>
       </c>
       <c r="C8" s="4" t="n">
-        <v>-68.87941661999031</v>
+        <v>-66.67474152497556</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>544.2465136081419</v>
+        <v>566.1520805035666</v>
       </c>
       <c r="F8" s="3" t="n">
         <v>-2</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>108.3014631503573</v>
+        <v>148.8217544533976</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>-285.2750910693468</v>
+        <v>-240.1834510322442</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>501.8780173700615</v>
+        <v>537.8269599390394</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>-2</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>1071.068814352604</v>
+        <v>1075.781280919428</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>-1280.145420813266</v>
+        <v>-1246.052270742946</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>3422.283049518474</v>
+        <v>3397.614832581803</v>
       </c>
       <c r="P8" s="3" t="n">
         <v>-2</v>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>765.2423271806319</v>
+        <v>781.7539475420282</v>
       </c>
       <c r="R8" s="4" t="n">
-        <v>-244.1677962412175</v>
+        <v>-226.7895164818163</v>
       </c>
       <c r="S8" s="4" t="n">
-        <v>1774.652450602481</v>
+        <v>1790.297411565873</v>
       </c>
     </row>
     <row r="9">
@@ -7790,49 +8042,49 @@
         <v>-1</v>
       </c>
       <c r="B9" s="4" t="n">
-        <v>259.4606722845134</v>
+        <v>261.3020065588398</v>
       </c>
       <c r="C9" s="4" t="n">
-        <v>-1.005783345112036</v>
+        <v>-14.12712427332548</v>
       </c>
       <c r="D9" s="4" t="n">
-        <v>519.9271279141387</v>
+        <v>536.7311373910049</v>
       </c>
       <c r="F9" s="3" t="n">
         <v>-1</v>
       </c>
       <c r="G9" s="4" t="n">
-        <v>70.1399686376607</v>
+        <v>80.54349455838759</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>-588.5373845788448</v>
+        <v>-608.4401915743215</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>728.8173218541662</v>
+        <v>769.5271806910966</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>-1</v>
       </c>
       <c r="L9" s="4" t="n">
-        <v>725.3202433594715</v>
+        <v>731.1275810429223</v>
       </c>
       <c r="M9" s="4" t="n">
-        <v>-643.1508459211382</v>
+        <v>-561.4326238738294</v>
       </c>
       <c r="N9" s="4" t="n">
-        <v>2093.791332640081</v>
+        <v>2023.687785959674</v>
       </c>
       <c r="P9" s="3" t="n">
         <v>-1</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>45.79802697663581</v>
+        <v>69.60659259060193</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>-724.2329520351975</v>
+        <v>-745.6426720908221</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>815.8290059884691</v>
+        <v>884.855857272026</v>
       </c>
     </row>
     <row r="10">
@@ -7840,49 +8092,49 @@
         <v>0</v>
       </c>
       <c r="B10" s="4" t="n">
-        <v>431.3998580431041</v>
+        <v>433.8582693198843</v>
       </c>
       <c r="C10" s="4" t="n">
-        <v>-605.0571092213286</v>
+        <v>-581.3783921425088</v>
       </c>
       <c r="D10" s="4" t="n">
-        <v>1467.856825307537</v>
+        <v>1449.094930782277</v>
       </c>
       <c r="F10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>198.6868253105739</v>
+        <v>207.7311153609667</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>-210.8056403297888</v>
+        <v>-181.4081838224159</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>608.1792909509365</v>
+        <v>596.8704145443494</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>-170.2884977006686</v>
+        <v>-170.9936675756291</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>-889.0367996466554</v>
+        <v>-902.6078504069872</v>
       </c>
       <c r="N10" s="4" t="n">
-        <v>548.4598042453182</v>
+        <v>560.6205152557288</v>
       </c>
       <c r="P10" s="3" t="n">
         <v>0</v>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>22.25019095833002</v>
+        <v>30.78165803029079</v>
       </c>
       <c r="R10" s="4" t="n">
-        <v>-610.8906851379533</v>
+        <v>-581.8534032218931</v>
       </c>
       <c r="S10" s="4" t="n">
-        <v>655.3910670546132</v>
+        <v>643.4167192824748</v>
       </c>
     </row>
     <row r="11">
@@ -7890,49 +8142,49 @@
         <v>1</v>
       </c>
       <c r="B11" s="4" t="n">
-        <v>1337.851158430178</v>
+        <v>1338.312629696692</v>
       </c>
       <c r="C11" s="4" t="n">
-        <v>-289.2741215176795</v>
+        <v>-342.5099964993788</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>2964.976438378035</v>
+        <v>3019.135255892762</v>
       </c>
       <c r="F11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>308.7693352275162</v>
+        <v>315.4158556770799</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>-1249.914257070284</v>
+        <v>-1276.568768155729</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>1867.452927525317</v>
+        <v>1907.400479509888</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>1434.83626841344</v>
+        <v>1431.134617991675</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>266.4367968634756</v>
+        <v>228.1121732136821</v>
       </c>
       <c r="N11" s="4" t="n">
-        <v>2603.235739963404</v>
+        <v>2634.157062769669</v>
       </c>
       <c r="P11" s="3" t="n">
         <v>1</v>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>-1173.880788578548</v>
+        <v>-1175.27808595632</v>
       </c>
       <c r="R11" s="4" t="n">
-        <v>-4862.202450246894</v>
+        <v>-4824.674690655798</v>
       </c>
       <c r="S11" s="4" t="n">
-        <v>2514.440873089798</v>
+        <v>2474.118518743159</v>
       </c>
     </row>
     <row r="12">
@@ -7940,49 +8192,49 @@
         <v>2</v>
       </c>
       <c r="B12" s="4" t="n">
-        <v>1893.883270313508</v>
+        <v>1892.620095363764</v>
       </c>
       <c r="C12" s="4" t="n">
-        <v>-1242.798307454353</v>
+        <v>-985.4289557177917</v>
       </c>
       <c r="D12" s="4" t="n">
-        <v>5030.564848081369</v>
+        <v>4770.66914644532</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>2</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>637.4837316720175</v>
+        <v>642.8994349101745</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>-1852.689574151517</v>
+        <v>-1809.335245637892</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>3127.657037495552</v>
+        <v>3095.134115458241</v>
       </c>
       <c r="K12" s="3" t="n">
         <v>2</v>
       </c>
       <c r="L12" s="4" t="n">
-        <v>1812.2012056202</v>
+        <v>1806.368091629098</v>
       </c>
       <c r="M12" s="4" t="n">
-        <v>532.4414628688435</v>
+        <v>607.7395683228544</v>
       </c>
       <c r="N12" s="4" t="n">
-        <v>3091.960948371556</v>
+        <v>3004.99661493534</v>
       </c>
       <c r="P12" s="3" t="n">
         <v>2</v>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>-1627.509882364014</v>
+        <v>-1633.62248542773</v>
       </c>
       <c r="R12" s="4" t="n">
-        <v>-8218.092594095318</v>
+        <v>-8395.98140629001</v>
       </c>
       <c r="S12" s="4" t="n">
-        <v>4963.072829367291</v>
+        <v>5128.736435434549</v>
       </c>
     </row>
     <row r="13">
@@ -7990,49 +8242,49 @@
         <v>3</v>
       </c>
       <c r="B13" s="4" t="n">
-        <v>2238.2596177321</v>
+        <v>2236.468290606154</v>
       </c>
       <c r="C13" s="4" t="n">
-        <v>-745.3116748834077</v>
+        <v>-787.5227722351865</v>
       </c>
       <c r="D13" s="4" t="n">
-        <v>5221.830910347608</v>
+        <v>5260.459353447495</v>
       </c>
       <c r="F13" s="3" t="n">
         <v>3</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>794.4208963857735</v>
+        <v>802.2652138708379</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>-944.5150807740246</v>
+        <v>-911.0840472924181</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>2533.356873545571</v>
+        <v>2515.614475034094</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>3</v>
       </c>
       <c r="L13" s="4" t="n">
-        <v>2487.806412981174</v>
+        <v>2479.783946902251</v>
       </c>
       <c r="M13" s="4" t="n">
-        <v>-326.4538492511961</v>
+        <v>-447.8195367490616</v>
       </c>
       <c r="N13" s="4" t="n">
-        <v>5302.066675213544</v>
+        <v>5407.387430553564</v>
       </c>
       <c r="P13" s="3" t="n">
         <v>3</v>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>-894.5610101219845</v>
+        <v>-908.2783776301214</v>
       </c>
       <c r="R13" s="4" t="n">
-        <v>-5410.219785385249</v>
+        <v>-5344.155737514068</v>
       </c>
       <c r="S13" s="4" t="n">
-        <v>3621.09776514128</v>
+        <v>3527.598982253826</v>
       </c>
     </row>
     <row r="14">
@@ -8040,49 +8292,49 @@
         <v>4</v>
       </c>
       <c r="B14" s="4" t="n">
-        <v>2371.635712360988</v>
+        <v>2369.094874860609</v>
       </c>
       <c r="C14" s="4" t="n">
-        <v>-684.5076491782434</v>
+        <v>-607.7445538925417</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>5427.779073900219</v>
+        <v>5345.93430361376</v>
       </c>
       <c r="F14" s="3" t="n">
         <v>4</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>1602.270465811529</v>
+        <v>1618.925816379521</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>220.6863460980383</v>
+        <v>246.4841136071559</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>2983.854585525019</v>
+        <v>2991.367519151886</v>
       </c>
       <c r="K14" s="3" t="n">
         <v>4</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3790.543591450753</v>
+        <v>3780.152280643041</v>
       </c>
       <c r="M14" s="4" t="n">
-        <v>-47.04575145324179</v>
+        <v>553.9518213194469</v>
       </c>
       <c r="N14" s="4" t="n">
-        <v>7628.132934354747</v>
+        <v>7006.352739966635</v>
       </c>
       <c r="P14" s="3" t="n">
         <v>4</v>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>1584.179183865232</v>
+        <v>1572.096832527938</v>
       </c>
       <c r="R14" s="4" t="n">
-        <v>-604.9405522004458</v>
+        <v>-658.5459267568312</v>
       </c>
       <c r="S14" s="4" t="n">
-        <v>3773.298919930909</v>
+        <v>3802.739591812708</v>
       </c>
     </row>
     <row r="15">
@@ -8090,49 +8342,49 @@
         <v>5</v>
       </c>
       <c r="B15" s="4" t="n">
-        <v>3789.577424195807</v>
+        <v>3790.307014415552</v>
       </c>
       <c r="C15" s="4" t="n">
-        <v>-332.2532765639407</v>
+        <v>-336.7846548082334</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>7911.408124955555</v>
+        <v>7917.398683639337</v>
       </c>
       <c r="F15" s="3" t="n">
         <v>5</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>4356.939015456991</v>
+        <v>4400.07479349951</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>441.4712463636583</v>
+        <v>301.1726008021224</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>8272.406784550323</v>
+        <v>8498.976986196896</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>5</v>
       </c>
       <c r="L15" s="4" t="n">
-        <v>5909.873884574686</v>
+        <v>5896.969872531055</v>
       </c>
       <c r="M15" s="4" t="n">
-        <v>2799.048376788711</v>
+        <v>2434.420648332713</v>
       </c>
       <c r="N15" s="4" t="n">
-        <v>9020.699392360661</v>
+        <v>9359.519096729398</v>
       </c>
       <c r="P15" s="3" t="n">
         <v>5</v>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>6706.247289128827</v>
+        <v>6699.053047711333</v>
       </c>
       <c r="R15" s="4" t="n">
-        <v>328.4639461290453</v>
+        <v>-3089.044122757835</v>
       </c>
       <c r="S15" s="4" t="n">
-        <v>13084.03063212861</v>
+        <v>16487.1502181805</v>
       </c>
     </row>
     <row r="16">
@@ -8140,49 +8392,49 @@
         <v>6</v>
       </c>
       <c r="B16" s="4" t="n">
-        <v>1171.75929132439</v>
+        <v>1193.183422878514</v>
       </c>
       <c r="C16" s="4" t="n">
-        <v>-5299.21744332563</v>
+        <v>-9096.306106279088</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>7642.73602597441</v>
+        <v>11482.67295203612</v>
       </c>
       <c r="F16" s="3" t="n">
         <v>6</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>3866.547576572173</v>
+        <v>3982.895214493728</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>2695.934137275353</v>
+        <v>2855.091860645132</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>5037.161015868993</v>
+        <v>5110.698568342324</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>6</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>5291.34601525855</v>
+        <v>5274.420951544332</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>4399.338312115564</v>
+        <v>4390.242954715131</v>
       </c>
       <c r="N16" s="4" t="n">
-        <v>6183.353718401537</v>
+        <v>6158.598948373533</v>
       </c>
       <c r="P16" s="3" t="n">
         <v>6</v>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>3675.567460317461</v>
+        <v>3675.091468253968</v>
       </c>
       <c r="R16" s="4" t="n">
-        <v>2553.361488016355</v>
+        <v>2534.939616073263</v>
       </c>
       <c r="S16" s="4" t="n">
-        <v>4797.773432618566</v>
+        <v>4815.243320434673</v>
       </c>
     </row>
     <row r="17">
@@ -8190,25 +8442,25 @@
         <v>7</v>
       </c>
       <c r="B17" s="4" t="n">
-        <v>-2873.128499930604</v>
+        <v>-2805.420798542867</v>
       </c>
       <c r="C17" s="4" t="n">
-        <v>-3830.766373238949</v>
+        <v>-3737.643041821978</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>-1915.490626622258</v>
+        <v>-1873.198555263757</v>
       </c>
       <c r="F17" s="3" t="n">
         <v>7</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>4566.593923611112</v>
+        <v>4833.089068100358</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>2978.664647818432</v>
+        <v>3497.303301451326</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>6154.523199403791</v>
+        <v>6168.874834749391</v>
       </c>
     </row>
   </sheetData>
